--- a/research/traditional_assets/database/data/chile/chile_machinery.xlsx
+++ b/research/traditional_assets/database/data/chile/chile_machinery.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.102153010567203</v>
+        <v>0.1019100474386715</v>
       </c>
       <c r="C2">
-        <v>24.58482870877758</v>
+        <v>24.43163300774429</v>
       </c>
       <c r="D2">
-        <v>22.79482870877758</v>
+        <v>22.89353300774429</v>
       </c>
       <c r="E2">
-        <v>-2.89</v>
+        <v>-2.6381</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.2519</v>
       </c>
       <c r="G2">
         <v>1.79</v>
@@ -1451,28 +1451,28 @@
         <v>0.828</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.01267057</v>
       </c>
       <c r="N2">
-        <v>0.828</v>
+        <v>0.8153294299999999</v>
       </c>
       <c r="O2">
-        <v>0.22356</v>
+        <v>0.2201389461</v>
       </c>
       <c r="P2">
-        <v>0.60444</v>
+        <v>0.5951904839</v>
       </c>
       <c r="Q2">
-        <v>0.68044</v>
+        <v>0.6711904839</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.102153010567203</v>
+        <v>0.102568542867345</v>
       </c>
       <c r="T2">
-        <v>1.032125178898191</v>
+        <v>1.039735798904208</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>65.34828346317489</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1019100474386715</v>
+        <v>0.1016670843101401</v>
       </c>
       <c r="C3">
-        <v>24.43163300774429</v>
+        <v>24.27929582673482</v>
       </c>
       <c r="D3">
-        <v>22.89353300774429</v>
+        <v>22.99309582673482</v>
       </c>
       <c r="E3">
-        <v>-2.6381</v>
+        <v>-2.3862</v>
       </c>
       <c r="F3">
-        <v>0.2519</v>
+        <v>0.5038</v>
       </c>
       <c r="G3">
         <v>1.79</v>
@@ -1533,28 +1533,28 @@
         <v>0.828</v>
       </c>
       <c r="M3">
-        <v>0.01267057</v>
+        <v>0.02534114</v>
       </c>
       <c r="N3">
-        <v>0.8153294299999999</v>
+        <v>0.80265886</v>
       </c>
       <c r="O3">
-        <v>0.2201389461</v>
+        <v>0.2167178922</v>
       </c>
       <c r="P3">
-        <v>0.5951904839</v>
+        <v>0.5859409677999999</v>
       </c>
       <c r="Q3">
-        <v>0.6711904839</v>
+        <v>0.6619409678</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.102568542867345</v>
+        <v>0.1029925554185103</v>
       </c>
       <c r="T3">
-        <v>1.039735798904208</v>
+        <v>1.047501737685858</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>65.34828346317489</v>
+        <v>32.67414173158745</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1016670843101401</v>
+        <v>0.1014241211816086</v>
       </c>
       <c r="C4">
-        <v>24.27929582673482</v>
+        <v>24.12782841565516</v>
       </c>
       <c r="D4">
-        <v>22.99309582673482</v>
+        <v>23.09352841565516</v>
       </c>
       <c r="E4">
-        <v>-2.3862</v>
+        <v>-2.1343</v>
       </c>
       <c r="F4">
-        <v>0.5038</v>
+        <v>0.7557</v>
       </c>
       <c r="G4">
         <v>1.79</v>
@@ -1615,28 +1615,28 @@
         <v>0.828</v>
       </c>
       <c r="M4">
-        <v>0.02534114</v>
+        <v>0.03801171</v>
       </c>
       <c r="N4">
-        <v>0.80265886</v>
+        <v>0.7899882899999999</v>
       </c>
       <c r="O4">
-        <v>0.2167178922</v>
+        <v>0.2132968383</v>
       </c>
       <c r="P4">
-        <v>0.5859409677999999</v>
+        <v>0.5766914516999999</v>
       </c>
       <c r="Q4">
-        <v>0.6619409678</v>
+        <v>0.6526914517</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1029925554185103</v>
+        <v>0.1034253104965037</v>
       </c>
       <c r="T4">
-        <v>1.047501737685858</v>
+        <v>1.055427798916614</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>32.67414173158745</v>
+        <v>21.78276115439163</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1014241211816086</v>
+        <v>0.1011811580530772</v>
       </c>
       <c r="C5">
-        <v>24.12782841565516</v>
+        <v>23.97724222182945</v>
       </c>
       <c r="D5">
-        <v>23.09352841565516</v>
+        <v>23.19484222182945</v>
       </c>
       <c r="E5">
-        <v>-2.1343</v>
+        <v>-1.8824</v>
       </c>
       <c r="F5">
-        <v>0.7557</v>
+        <v>1.0076</v>
       </c>
       <c r="G5">
         <v>1.79</v>
@@ -1697,28 +1697,28 @@
         <v>0.828</v>
       </c>
       <c r="M5">
-        <v>0.03801171</v>
+        <v>0.05068228</v>
       </c>
       <c r="N5">
-        <v>0.7899882899999999</v>
+        <v>0.77731772</v>
       </c>
       <c r="O5">
-        <v>0.2132968383</v>
+        <v>0.2098757844</v>
       </c>
       <c r="P5">
-        <v>0.5766914516999999</v>
+        <v>0.5674419356</v>
       </c>
       <c r="Q5">
-        <v>0.6526914517</v>
+        <v>0.6434419356000001</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1034253104965037</v>
+        <v>0.1038670813052887</v>
       </c>
       <c r="T5">
-        <v>1.055427798916614</v>
+        <v>1.063518986423011</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>21.78276115439163</v>
+        <v>16.33707086579372</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1011811580530772</v>
+        <v>0.1009381949245457</v>
       </c>
       <c r="C6">
-        <v>23.97724222182945</v>
+        <v>23.82754889434967</v>
       </c>
       <c r="D6">
-        <v>23.19484222182945</v>
+        <v>23.29704889434967</v>
       </c>
       <c r="E6">
-        <v>-1.8824</v>
+        <v>-1.6305</v>
       </c>
       <c r="F6">
-        <v>1.0076</v>
+        <v>1.2595</v>
       </c>
       <c r="G6">
         <v>1.79</v>
@@ -1779,28 +1779,28 @@
         <v>0.828</v>
       </c>
       <c r="M6">
-        <v>0.05068228</v>
+        <v>0.06335285</v>
       </c>
       <c r="N6">
-        <v>0.77731772</v>
+        <v>0.7646471499999999</v>
       </c>
       <c r="O6">
-        <v>0.2098757844</v>
+        <v>0.2064547305</v>
       </c>
       <c r="P6">
-        <v>0.5674419356</v>
+        <v>0.5581924195</v>
       </c>
       <c r="Q6">
-        <v>0.6434419356000001</v>
+        <v>0.6341924195</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1038670813052887</v>
+        <v>0.1043181525521534</v>
       </c>
       <c r="T6">
-        <v>1.063518986423011</v>
+        <v>1.071780514719016</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>16.33707086579372</v>
+        <v>13.06965669263498</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1009381949245457</v>
+        <v>0.1007609317960143</v>
       </c>
       <c r="C7">
-        <v>23.82754889434967</v>
+        <v>23.65078786375233</v>
       </c>
       <c r="D7">
-        <v>23.29704889434967</v>
+        <v>23.37218786375233</v>
       </c>
       <c r="E7">
-        <v>-1.6305</v>
+        <v>-1.3786</v>
       </c>
       <c r="F7">
-        <v>1.2595</v>
+        <v>1.5114</v>
       </c>
       <c r="G7">
         <v>1.79</v>
@@ -1861,45 +1861,45 @@
         <v>0.828</v>
       </c>
       <c r="M7">
-        <v>0.06335285</v>
+        <v>0.07829052000000002</v>
       </c>
       <c r="N7">
-        <v>0.7646471499999999</v>
+        <v>0.7497094799999999</v>
       </c>
       <c r="O7">
-        <v>0.2064547305</v>
+        <v>0.2024215596</v>
       </c>
       <c r="P7">
-        <v>0.5581924195</v>
+        <v>0.5472879204</v>
       </c>
       <c r="Q7">
-        <v>0.6341924195</v>
+        <v>0.6232879204</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1043181525521534</v>
+        <v>0.1047788210595896</v>
       </c>
       <c r="T7">
-        <v>1.071780514719016</v>
+        <v>1.080217820212809</v>
       </c>
       <c r="U7">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V7">
         <v>0.27</v>
       </c>
       <c r="W7">
-        <v>0.03671899999999999</v>
+        <v>0.037814</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y7">
-        <v>13.06965669263498</v>
+        <v>10.5759931087442</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1007609317960143</v>
+        <v>0.1006157886674828</v>
       </c>
       <c r="C8">
-        <v>23.65078786375233</v>
+        <v>23.46077354577265</v>
       </c>
       <c r="D8">
-        <v>23.37218786375233</v>
+        <v>23.43407354577266</v>
       </c>
       <c r="E8">
-        <v>-1.3786</v>
+        <v>-1.1267</v>
       </c>
       <c r="F8">
-        <v>1.5114</v>
+        <v>1.7633</v>
       </c>
       <c r="G8">
         <v>1.79</v>
@@ -1943,45 +1943,45 @@
         <v>0.828</v>
       </c>
       <c r="M8">
-        <v>0.07829052</v>
+        <v>0.09433654999999999</v>
       </c>
       <c r="N8">
-        <v>0.7497094799999999</v>
+        <v>0.73366345</v>
       </c>
       <c r="O8">
-        <v>0.2024215596</v>
+        <v>0.1980891315</v>
       </c>
       <c r="P8">
-        <v>0.5472879204</v>
+        <v>0.5355743184999999</v>
       </c>
       <c r="Q8">
-        <v>0.6232879204</v>
+        <v>0.6115743185</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1047788210595896</v>
+        <v>0.1052493964166482</v>
       </c>
       <c r="T8">
-        <v>1.080217820212809</v>
+        <v>1.088836573136576</v>
       </c>
       <c r="U8">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V8">
         <v>0.27</v>
       </c>
       <c r="W8">
-        <v>0.037814</v>
+        <v>0.039055</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y8">
-        <v>10.5759931087442</v>
+        <v>8.777085869686776</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1006157886674828</v>
+        <v>0.1003961855389514</v>
       </c>
       <c r="C9">
-        <v>23.46077354577266</v>
+        <v>23.30313280242377</v>
       </c>
       <c r="D9">
-        <v>23.43407354577266</v>
+        <v>23.52833280242377</v>
       </c>
       <c r="E9">
-        <v>-1.1267</v>
+        <v>-0.8748</v>
       </c>
       <c r="F9">
-        <v>1.7633</v>
+        <v>2.0152</v>
       </c>
       <c r="G9">
         <v>1.79</v>
@@ -2025,28 +2025,28 @@
         <v>0.828</v>
       </c>
       <c r="M9">
-        <v>0.09433655000000002</v>
+        <v>0.1078132</v>
       </c>
       <c r="N9">
-        <v>0.7336634499999999</v>
+        <v>0.7201868</v>
       </c>
       <c r="O9">
-        <v>0.1980891315</v>
+        <v>0.194450436</v>
       </c>
       <c r="P9">
-        <v>0.5355743184999999</v>
+        <v>0.525736364</v>
       </c>
       <c r="Q9">
-        <v>0.6115743185</v>
+        <v>0.6017363640000001</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1052493964166482</v>
+        <v>0.1057302016727732</v>
       </c>
       <c r="T9">
-        <v>1.088836573136576</v>
+        <v>1.097642690254337</v>
       </c>
       <c r="U9">
         <v>0.0535</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>8.777085869686772</v>
+        <v>7.679950135975929</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1003961855389514</v>
+        <v>0.1002291424104199</v>
       </c>
       <c r="C10">
-        <v>23.30313280242377</v>
+        <v>23.12344129490397</v>
       </c>
       <c r="D10">
-        <v>23.52833280242377</v>
+        <v>23.60054129490397</v>
       </c>
       <c r="E10">
-        <v>-0.8748</v>
+        <v>-0.6229</v>
       </c>
       <c r="F10">
-        <v>2.0152</v>
+        <v>2.2671</v>
       </c>
       <c r="G10">
         <v>1.79</v>
@@ -2107,45 +2107,45 @@
         <v>0.828</v>
       </c>
       <c r="M10">
-        <v>0.1078132</v>
+        <v>0.12310353</v>
       </c>
       <c r="N10">
-        <v>0.7201868</v>
+        <v>0.70489647</v>
       </c>
       <c r="O10">
-        <v>0.194450436</v>
+        <v>0.1903220469</v>
       </c>
       <c r="P10">
-        <v>0.525736364</v>
+        <v>0.5145744231</v>
       </c>
       <c r="Q10">
-        <v>0.6017363640000001</v>
+        <v>0.5905744231000001</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1057302016727732</v>
+        <v>0.1062215740773845</v>
       </c>
       <c r="T10">
-        <v>1.097642690254337</v>
+        <v>1.106642348407654</v>
       </c>
       <c r="U10">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V10">
         <v>0.27</v>
       </c>
       <c r="W10">
-        <v>0.039055</v>
+        <v>0.039639</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y10">
-        <v>7.679950135975929</v>
+        <v>6.726045954977895</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1002291424104199</v>
+        <v>0.1000883792818885</v>
       </c>
       <c r="C11">
-        <v>23.12344129490397</v>
+        <v>22.9327346123625</v>
       </c>
       <c r="D11">
-        <v>23.60054129490397</v>
+        <v>23.6617346123625</v>
       </c>
       <c r="E11">
-        <v>-0.6229</v>
+        <v>-0.371</v>
       </c>
       <c r="F11">
-        <v>2.2671</v>
+        <v>2.519</v>
       </c>
       <c r="G11">
         <v>1.79</v>
@@ -2189,45 +2189,45 @@
         <v>0.828</v>
       </c>
       <c r="M11">
-        <v>0.12310353</v>
+        <v>0.1393007</v>
       </c>
       <c r="N11">
-        <v>0.70489647</v>
+        <v>0.6886992999999999</v>
       </c>
       <c r="O11">
-        <v>0.1903220469</v>
+        <v>0.185948811</v>
       </c>
       <c r="P11">
-        <v>0.5145744231</v>
+        <v>0.5027504889999999</v>
       </c>
       <c r="Q11">
-        <v>0.5905744231000001</v>
+        <v>0.5787504889999999</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1062215740773845</v>
+        <v>0.106723865868765</v>
       </c>
       <c r="T11">
-        <v>1.106642348407654</v>
+        <v>1.115841998964378</v>
       </c>
       <c r="U11">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V11">
         <v>0.27</v>
       </c>
       <c r="W11">
-        <v>0.039639</v>
+        <v>0.040369</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y11">
-        <v>6.726045954977895</v>
+        <v>5.943975873775221</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1000883792818885</v>
+        <v>0.09988191615335702</v>
       </c>
       <c r="C12">
-        <v>22.9327346123625</v>
+        <v>22.77116565279192</v>
       </c>
       <c r="D12">
-        <v>23.6617346123625</v>
+        <v>23.75206565279192</v>
       </c>
       <c r="E12">
-        <v>-0.371</v>
+        <v>-0.1191</v>
       </c>
       <c r="F12">
-        <v>2.519</v>
+        <v>2.7709</v>
       </c>
       <c r="G12">
         <v>1.79</v>
@@ -2271,28 +2271,28 @@
         <v>0.828</v>
       </c>
       <c r="M12">
-        <v>0.1393007</v>
+        <v>0.15323077</v>
       </c>
       <c r="N12">
-        <v>0.6886992999999999</v>
+        <v>0.6747692299999999</v>
       </c>
       <c r="O12">
-        <v>0.185948811</v>
+        <v>0.1821876921</v>
       </c>
       <c r="P12">
-        <v>0.5027504889999999</v>
+        <v>0.4925815378999999</v>
       </c>
       <c r="Q12">
-        <v>0.5787504889999999</v>
+        <v>0.5685815379</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.106723865868765</v>
+        <v>0.1072374451161315</v>
       </c>
       <c r="T12">
-        <v>1.115841998964378</v>
+        <v>1.125248383241477</v>
       </c>
       <c r="U12">
         <v>0.0553</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>5.943975873775221</v>
+        <v>5.403614430704746</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.09988191615335702</v>
+        <v>0.09967545302482558</v>
       </c>
       <c r="C13">
-        <v>22.77116565279192</v>
+        <v>22.61028903187144</v>
       </c>
       <c r="D13">
-        <v>23.75206565279192</v>
+        <v>23.84308903187144</v>
       </c>
       <c r="E13">
-        <v>-0.1191</v>
+        <v>0.1328</v>
       </c>
       <c r="F13">
-        <v>2.7709</v>
+        <v>3.0228</v>
       </c>
       <c r="G13">
         <v>1.79</v>
@@ -2353,28 +2353,28 @@
         <v>0.828</v>
       </c>
       <c r="M13">
-        <v>0.15323077</v>
+        <v>0.16716084</v>
       </c>
       <c r="N13">
-        <v>0.6747692299999999</v>
+        <v>0.66083916</v>
       </c>
       <c r="O13">
-        <v>0.1821876921</v>
+        <v>0.1784265732</v>
       </c>
       <c r="P13">
-        <v>0.4925815378999999</v>
+        <v>0.4824125868</v>
       </c>
       <c r="Q13">
-        <v>0.5685815379</v>
+        <v>0.5584125868000001</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1072374451161315</v>
+        <v>0.10776269661912</v>
       </c>
       <c r="T13">
-        <v>1.125248383241477</v>
+        <v>1.13486854897942</v>
       </c>
       <c r="U13">
         <v>0.0553</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>5.403614430704746</v>
+        <v>4.953313228146017</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.09967545302482558</v>
+        <v>0.09946898989629413</v>
       </c>
       <c r="C14">
-        <v>22.61028903187144</v>
+        <v>22.45011273982433</v>
       </c>
       <c r="D14">
-        <v>23.84308903187144</v>
+        <v>23.93481273982433</v>
       </c>
       <c r="E14">
-        <v>0.1328</v>
+        <v>0.3847</v>
       </c>
       <c r="F14">
-        <v>3.0228</v>
+        <v>3.2747</v>
       </c>
       <c r="G14">
         <v>1.79</v>
@@ -2435,28 +2435,28 @@
         <v>0.828</v>
       </c>
       <c r="M14">
-        <v>0.16716084</v>
+        <v>0.18109091</v>
       </c>
       <c r="N14">
-        <v>0.66083916</v>
+        <v>0.64690909</v>
       </c>
       <c r="O14">
-        <v>0.1784265732</v>
+        <v>0.1746654543</v>
       </c>
       <c r="P14">
-        <v>0.4824125868</v>
+        <v>0.4722436356999999</v>
       </c>
       <c r="Q14">
-        <v>0.5584125868000001</v>
+        <v>0.5482436357</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.10776269661912</v>
+        <v>0.1083000228693036</v>
       </c>
       <c r="T14">
-        <v>1.13486854897942</v>
+        <v>1.144709867952718</v>
       </c>
       <c r="U14">
         <v>0.0553</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>4.953313228146017</v>
+        <v>4.572289133673246</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.09946898989629413</v>
+        <v>0.09951802676776267</v>
       </c>
       <c r="C15">
-        <v>22.45011273982433</v>
+        <v>22.17636368082928</v>
       </c>
       <c r="D15">
-        <v>23.93481273982433</v>
+        <v>23.91296368082928</v>
       </c>
       <c r="E15">
-        <v>0.3847</v>
+        <v>0.6366000000000005</v>
       </c>
       <c r="F15">
-        <v>3.2747</v>
+        <v>3.526600000000001</v>
       </c>
       <c r="G15">
         <v>1.79</v>
@@ -2517,45 +2517,45 @@
         <v>0.828</v>
       </c>
       <c r="M15">
-        <v>0.18109091</v>
+        <v>0.20383748</v>
       </c>
       <c r="N15">
-        <v>0.64690909</v>
+        <v>0.6241625199999999</v>
       </c>
       <c r="O15">
-        <v>0.1746654543</v>
+        <v>0.1685238804</v>
       </c>
       <c r="P15">
-        <v>0.4722436356999999</v>
+        <v>0.4556386396</v>
       </c>
       <c r="Q15">
-        <v>0.5482436357</v>
+        <v>0.5316386396</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1083000228693036</v>
+        <v>0.1088498450787938</v>
       </c>
       <c r="T15">
-        <v>1.144709867952718</v>
+        <v>1.154780054809116</v>
       </c>
       <c r="U15">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V15">
         <v>0.27</v>
       </c>
       <c r="W15">
-        <v>0.040369</v>
+        <v>0.042194</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y15">
-        <v>4.572289133673246</v>
+        <v>4.062059636922513</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.09951802676776267</v>
+        <v>0.09971306363923126</v>
       </c>
       <c r="C16">
-        <v>22.17636368082928</v>
+        <v>21.83795571209168</v>
       </c>
       <c r="D16">
-        <v>23.91296368082928</v>
+        <v>23.82645571209168</v>
       </c>
       <c r="E16">
-        <v>0.6366000000000005</v>
+        <v>0.8885000000000005</v>
       </c>
       <c r="F16">
-        <v>3.526600000000001</v>
+        <v>3.778500000000001</v>
       </c>
       <c r="G16">
         <v>1.79</v>
@@ -2599,45 +2599,45 @@
         <v>0.828</v>
       </c>
       <c r="M16">
-        <v>0.20383748</v>
+        <v>0.2316220500000001</v>
       </c>
       <c r="N16">
-        <v>0.6241625199999999</v>
+        <v>0.5963779499999999</v>
       </c>
       <c r="O16">
-        <v>0.1685238804</v>
+        <v>0.1610220465</v>
       </c>
       <c r="P16">
-        <v>0.4556386396</v>
+        <v>0.4353559035</v>
       </c>
       <c r="Q16">
-        <v>0.5316386396</v>
+        <v>0.5113559035</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1088498450787938</v>
+        <v>0.1094126042814485</v>
       </c>
       <c r="T16">
-        <v>1.154780054809116</v>
+        <v>1.165087187238605</v>
       </c>
       <c r="U16">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V16">
         <v>0.27</v>
       </c>
       <c r="W16">
-        <v>0.042194</v>
+        <v>0.044749</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y16">
-        <v>4.062059636922513</v>
+        <v>3.574789187816962</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.09971306363923126</v>
+        <v>0.09987744051069979</v>
       </c>
       <c r="C17">
-        <v>21.83795571209168</v>
+        <v>21.51363145881434</v>
       </c>
       <c r="D17">
-        <v>23.82645571209168</v>
+        <v>23.75403145881434</v>
       </c>
       <c r="E17">
-        <v>0.8885000000000001</v>
+        <v>1.1404</v>
       </c>
       <c r="F17">
-        <v>3.7785</v>
+        <v>4.0304</v>
       </c>
       <c r="G17">
         <v>1.79</v>
@@ -2681,45 +2681,45 @@
         <v>0.828</v>
       </c>
       <c r="M17">
-        <v>0.23162205</v>
+        <v>0.25834864</v>
       </c>
       <c r="N17">
-        <v>0.5963779499999999</v>
+        <v>0.5696513599999999</v>
       </c>
       <c r="O17">
-        <v>0.1610220465</v>
+        <v>0.1538058672</v>
       </c>
       <c r="P17">
-        <v>0.4353559035</v>
+        <v>0.4158454927999999</v>
       </c>
       <c r="Q17">
-        <v>0.5113559035</v>
+        <v>0.4918454928</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1094126042814485</v>
+        <v>0.1099887625127378</v>
       </c>
       <c r="T17">
-        <v>1.165087187238605</v>
+        <v>1.175639727583083</v>
       </c>
       <c r="U17">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V17">
         <v>0.27</v>
       </c>
       <c r="W17">
-        <v>0.044749</v>
+        <v>0.046793</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y17">
-        <v>3.574789187816962</v>
+        <v>3.204971390598379</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.09987744051069979</v>
+        <v>0.09973521738216834</v>
       </c>
       <c r="C18">
-        <v>21.51363145881434</v>
+        <v>21.32436906061298</v>
       </c>
       <c r="D18">
-        <v>23.75403145881434</v>
+        <v>23.81666906061298</v>
       </c>
       <c r="E18">
-        <v>1.1404</v>
+        <v>1.3923</v>
       </c>
       <c r="F18">
-        <v>4.0304</v>
+        <v>4.2823</v>
       </c>
       <c r="G18">
         <v>1.79</v>
@@ -2763,28 +2763,28 @@
         <v>0.828</v>
       </c>
       <c r="M18">
-        <v>0.25834864</v>
+        <v>0.27449543</v>
       </c>
       <c r="N18">
-        <v>0.5696513599999999</v>
+        <v>0.5535045699999999</v>
       </c>
       <c r="O18">
-        <v>0.1538058672</v>
+        <v>0.1494462339</v>
       </c>
       <c r="P18">
-        <v>0.4158454927999999</v>
+        <v>0.4040583360999999</v>
       </c>
       <c r="Q18">
-        <v>0.4918454928</v>
+        <v>0.4800583360999999</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1099887625127378</v>
+        <v>0.1105788040749016</v>
       </c>
       <c r="T18">
-        <v>1.175639727583083</v>
+        <v>1.18644654600815</v>
       </c>
       <c r="U18">
         <v>0.0641</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>3.204971390598379</v>
+        <v>3.01644366173965</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.09973521738216834</v>
+        <v>0.1006179142536369</v>
       </c>
       <c r="C19">
-        <v>21.32436906061298</v>
+        <v>20.68896488036756</v>
       </c>
       <c r="D19">
-        <v>23.81666906061298</v>
+        <v>23.43316488036756</v>
       </c>
       <c r="E19">
-        <v>1.3923</v>
+        <v>1.644200000000001</v>
       </c>
       <c r="F19">
-        <v>4.2823</v>
+        <v>4.534200000000001</v>
       </c>
       <c r="G19">
         <v>1.79</v>
@@ -2845,45 +2845,45 @@
         <v>0.828</v>
       </c>
       <c r="M19">
-        <v>0.27449543</v>
+        <v>0.3260089800000001</v>
       </c>
       <c r="N19">
-        <v>0.5535045699999999</v>
+        <v>0.5019910199999998</v>
       </c>
       <c r="O19">
-        <v>0.1494462339</v>
+        <v>0.1355375754</v>
       </c>
       <c r="P19">
-        <v>0.4040583360999999</v>
+        <v>0.3664534445999998</v>
       </c>
       <c r="Q19">
-        <v>0.4800583360999999</v>
+        <v>0.4424534445999999</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1105788040749016</v>
+        <v>0.1111832368946791</v>
       </c>
       <c r="T19">
-        <v>1.18644654600815</v>
+        <v>1.197516945370413</v>
       </c>
       <c r="U19">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V19">
         <v>0.27</v>
       </c>
       <c r="W19">
-        <v>0.046793</v>
+        <v>0.05248700000000001</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y19">
-        <v>3.01644366173965</v>
+        <v>2.539807339049371</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1006179142536369</v>
+        <v>0.1010735611251054</v>
       </c>
       <c r="C20">
-        <v>20.68896488036755</v>
+        <v>20.24389389501744</v>
       </c>
       <c r="D20">
-        <v>23.43316488036755</v>
+        <v>23.23999389501744</v>
       </c>
       <c r="E20">
-        <v>1.6442</v>
+        <v>1.8961</v>
       </c>
       <c r="F20">
-        <v>4.5342</v>
+        <v>4.7861</v>
       </c>
       <c r="G20">
         <v>1.79</v>
@@ -2927,45 +2927,45 @@
         <v>0.828</v>
       </c>
       <c r="M20">
-        <v>0.3260089800000001</v>
+        <v>0.3627863800000001</v>
       </c>
       <c r="N20">
-        <v>0.50199102</v>
+        <v>0.4652136199999999</v>
       </c>
       <c r="O20">
-        <v>0.1355375754</v>
+        <v>0.1256076774</v>
       </c>
       <c r="P20">
-        <v>0.3664534446</v>
+        <v>0.3396059425999999</v>
       </c>
       <c r="Q20">
-        <v>0.4424534446</v>
+        <v>0.4156059425999999</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1111832368946791</v>
+        <v>0.1118025939816117</v>
       </c>
       <c r="T20">
-        <v>1.197516945370413</v>
+        <v>1.208860687926807</v>
       </c>
       <c r="U20">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V20">
         <v>0.27</v>
       </c>
       <c r="W20">
-        <v>0.05248700000000001</v>
+        <v>0.055334</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y20">
-        <v>2.539807339049372</v>
+        <v>2.282334855018537</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1010735611251054</v>
+        <v>0.101016747996574</v>
       </c>
       <c r="C21">
-        <v>20.24389389501744</v>
+        <v>20.01590578422014</v>
       </c>
       <c r="D21">
-        <v>23.23999389501744</v>
+        <v>23.26390578422015</v>
       </c>
       <c r="E21">
-        <v>1.8961</v>
+        <v>2.148</v>
       </c>
       <c r="F21">
-        <v>4.7861</v>
+        <v>5.038</v>
       </c>
       <c r="G21">
         <v>1.79</v>
@@ -3009,28 +3009,28 @@
         <v>0.828</v>
       </c>
       <c r="M21">
-        <v>0.3627863800000001</v>
+        <v>0.3818804000000001</v>
       </c>
       <c r="N21">
-        <v>0.4652136199999999</v>
+        <v>0.4461195999999999</v>
       </c>
       <c r="O21">
-        <v>0.1256076774</v>
+        <v>0.120452292</v>
       </c>
       <c r="P21">
-        <v>0.3396059425999999</v>
+        <v>0.3256673079999999</v>
       </c>
       <c r="Q21">
-        <v>0.4156059425999999</v>
+        <v>0.401667308</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1118025939816117</v>
+        <v>0.1124374349957175</v>
       </c>
       <c r="T21">
-        <v>1.208860687926807</v>
+        <v>1.220488024047111</v>
       </c>
       <c r="U21">
         <v>0.07580000000000001</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>2.282334855018537</v>
+        <v>2.16821811226761</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.101016747996574</v>
+        <v>0.1009599348680426</v>
       </c>
       <c r="C22">
-        <v>20.01590578422014</v>
+        <v>19.7879669305236</v>
       </c>
       <c r="D22">
-        <v>23.26390578422015</v>
+        <v>23.2878669305236</v>
       </c>
       <c r="E22">
-        <v>2.148</v>
+        <v>2.399900000000001</v>
       </c>
       <c r="F22">
-        <v>5.038</v>
+        <v>5.289900000000001</v>
       </c>
       <c r="G22">
         <v>1.79</v>
@@ -3091,28 +3091,28 @@
         <v>0.828</v>
       </c>
       <c r="M22">
-        <v>0.3818804000000001</v>
+        <v>0.4009744200000001</v>
       </c>
       <c r="N22">
-        <v>0.4461195999999999</v>
+        <v>0.4270255799999998</v>
       </c>
       <c r="O22">
-        <v>0.120452292</v>
+        <v>0.1152969066</v>
       </c>
       <c r="P22">
-        <v>0.3256673079999999</v>
+        <v>0.3117286733999999</v>
       </c>
       <c r="Q22">
-        <v>0.401667308</v>
+        <v>0.3877286733999999</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1124374349957175</v>
+        <v>0.1130883479342311</v>
       </c>
       <c r="T22">
-        <v>1.220488024047111</v>
+        <v>1.232409723107169</v>
       </c>
       <c r="U22">
         <v>0.07580000000000001</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>2.16821811226761</v>
+        <v>2.064969630731057</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1009599348680426</v>
+        <v>0.1031836417395111</v>
       </c>
       <c r="C23">
-        <v>19.7879669305236</v>
+        <v>18.63362525646035</v>
       </c>
       <c r="D23">
-        <v>23.2878669305236</v>
+        <v>22.38542525646035</v>
       </c>
       <c r="E23">
-        <v>2.3999</v>
+        <v>2.6518</v>
       </c>
       <c r="F23">
-        <v>5.2899</v>
+        <v>5.5418</v>
       </c>
       <c r="G23">
         <v>1.79</v>
@@ -3173,45 +3173,45 @@
         <v>0.828</v>
       </c>
       <c r="M23">
-        <v>0.4009744200000001</v>
+        <v>0.498762</v>
       </c>
       <c r="N23">
-        <v>0.4270255799999999</v>
+        <v>0.329238</v>
       </c>
       <c r="O23">
-        <v>0.1152969066</v>
+        <v>0.08889426</v>
       </c>
       <c r="P23">
-        <v>0.3117286733999999</v>
+        <v>0.24034374</v>
       </c>
       <c r="Q23">
-        <v>0.3877286734</v>
+        <v>0.31634374</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1130883479342311</v>
+        <v>0.1137559509480912</v>
       </c>
       <c r="T23">
-        <v>1.232409723107169</v>
+        <v>1.244637106758511</v>
       </c>
       <c r="U23">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V23">
         <v>0.27</v>
       </c>
       <c r="W23">
-        <v>0.055334</v>
+        <v>0.06569999999999999</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y23">
-        <v>2.064969630731057</v>
+        <v>1.66011043343318</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1031836417395111</v>
+        <v>0.1032304886109797</v>
       </c>
       <c r="C24">
-        <v>18.63362525646035</v>
+        <v>18.36346514471269</v>
       </c>
       <c r="D24">
-        <v>22.38542525646035</v>
+        <v>22.3671651447127</v>
       </c>
       <c r="E24">
-        <v>2.6518</v>
+        <v>2.9037</v>
       </c>
       <c r="F24">
-        <v>5.5418</v>
+        <v>5.7937</v>
       </c>
       <c r="G24">
         <v>1.79</v>
@@ -3255,28 +3255,28 @@
         <v>0.828</v>
       </c>
       <c r="M24">
-        <v>0.498762</v>
+        <v>0.521433</v>
       </c>
       <c r="N24">
-        <v>0.329238</v>
+        <v>0.3065669999999999</v>
       </c>
       <c r="O24">
-        <v>0.08889426</v>
+        <v>0.08277308999999998</v>
       </c>
       <c r="P24">
-        <v>0.24034374</v>
+        <v>0.2237939099999999</v>
       </c>
       <c r="Q24">
-        <v>0.31634374</v>
+        <v>0.29979391</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1137559509480912</v>
+        <v>0.1144408942999736</v>
       </c>
       <c r="T24">
-        <v>1.244637106758511</v>
+        <v>1.257182084790407</v>
       </c>
       <c r="U24">
         <v>0.09</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>1.66011043343318</v>
+        <v>1.587931718936086</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1032304886109797</v>
+        <v>0.1032773354824482</v>
       </c>
       <c r="C25">
-        <v>18.36346514471269</v>
+        <v>18.09333479875364</v>
       </c>
       <c r="D25">
-        <v>22.3671651447127</v>
+        <v>22.34893479875364</v>
       </c>
       <c r="E25">
-        <v>2.9037</v>
+        <v>3.155600000000001</v>
       </c>
       <c r="F25">
-        <v>5.7937</v>
+        <v>6.045600000000001</v>
       </c>
       <c r="G25">
         <v>1.79</v>
@@ -3337,28 +3337,28 @@
         <v>0.828</v>
       </c>
       <c r="M25">
-        <v>0.521433</v>
+        <v>0.544104</v>
       </c>
       <c r="N25">
-        <v>0.3065669999999999</v>
+        <v>0.2838959999999999</v>
       </c>
       <c r="O25">
-        <v>0.08277308999999998</v>
+        <v>0.07665191999999998</v>
       </c>
       <c r="P25">
-        <v>0.2237939099999999</v>
+        <v>0.2072440799999999</v>
       </c>
       <c r="Q25">
-        <v>0.29979391</v>
+        <v>0.28324408</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1144408942999736</v>
+        <v>0.1151438624769055</v>
       </c>
       <c r="T25">
-        <v>1.257182084790407</v>
+        <v>1.270057193823143</v>
       </c>
       <c r="U25">
         <v>0.09</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>1.587931718936086</v>
+        <v>1.521767897313749</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1032773354824482</v>
+        <v>0.1151211789067857</v>
       </c>
       <c r="C26">
-        <v>18.09333479875364</v>
+        <v>14.02301611875548</v>
       </c>
       <c r="D26">
-        <v>22.34893479875364</v>
+        <v>18.53051611875548</v>
       </c>
       <c r="E26">
-        <v>3.1556</v>
+        <v>3.4075</v>
       </c>
       <c r="F26">
-        <v>6.0456</v>
+        <v>6.2975</v>
       </c>
       <c r="G26">
         <v>1.79</v>
@@ -3419,45 +3419,45 @@
         <v>0.828</v>
       </c>
       <c r="M26">
-        <v>0.544104</v>
+        <v>0.9244730000000001</v>
       </c>
       <c r="N26">
-        <v>0.2838959999999999</v>
+        <v>-0.09647300000000014</v>
       </c>
       <c r="O26">
-        <v>0.07665191999999998</v>
+        <v>-0.02604771000000004</v>
       </c>
       <c r="P26">
-        <v>0.2072440799999999</v>
+        <v>-0.0704252900000001</v>
       </c>
       <c r="Q26">
-        <v>0.28324408</v>
+        <v>0.005574709999999969</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1151438624769055</v>
+        <v>0.1163948390452259</v>
       </c>
       <c r="T26">
-        <v>1.270057193823143</v>
+        <v>1.292969268996754</v>
       </c>
       <c r="U26">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V26">
-        <v>0.27</v>
+        <v>0.2418242609573238</v>
       </c>
       <c r="W26">
-        <v>0.06569999999999999</v>
+        <v>0.1113001984914649</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y26">
-        <v>1.521767897313749</v>
+        <v>0.8956454109530509</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1151211789067857</v>
+        <v>0.1161311789067856</v>
       </c>
       <c r="C27">
-        <v>14.02301611875548</v>
+        <v>13.50500624300965</v>
       </c>
       <c r="D27">
-        <v>18.53051611875548</v>
+        <v>18.26440624300965</v>
       </c>
       <c r="E27">
-        <v>3.4075</v>
+        <v>3.6594</v>
       </c>
       <c r="F27">
-        <v>6.2975</v>
+        <v>6.5494</v>
       </c>
       <c r="G27">
         <v>1.79</v>
@@ -3501,37 +3501,37 @@
         <v>0.828</v>
       </c>
       <c r="M27">
-        <v>0.9244730000000001</v>
+        <v>0.9614519200000001</v>
       </c>
       <c r="N27">
-        <v>-0.09647300000000014</v>
+        <v>-0.1334519200000002</v>
       </c>
       <c r="O27">
-        <v>-0.02604771000000004</v>
+        <v>-0.03603201840000005</v>
       </c>
       <c r="P27">
-        <v>-0.0704252900000001</v>
+        <v>-0.09741990160000012</v>
       </c>
       <c r="Q27">
-        <v>0.005574709999999969</v>
+        <v>-0.02141990160000005</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1163948390452259</v>
+        <v>0.1173488233566479</v>
       </c>
       <c r="T27">
-        <v>1.292969268996754</v>
+        <v>1.3104418266859</v>
       </c>
       <c r="U27">
         <v>0.1468</v>
       </c>
       <c r="V27">
-        <v>0.2418242609573238</v>
+        <v>0.2325233278435805</v>
       </c>
       <c r="W27">
-        <v>0.1113001984914649</v>
+        <v>0.1126655754725624</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>0.8956454109530509</v>
+        <v>0.8611975105317797</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1161311789067856</v>
+        <v>0.1171411789067856</v>
       </c>
       <c r="C28">
-        <v>13.50500624300965</v>
+        <v>12.99453117334977</v>
       </c>
       <c r="D28">
-        <v>18.26440624300965</v>
+        <v>18.00583117334977</v>
       </c>
       <c r="E28">
-        <v>3.6594</v>
+        <v>3.911300000000001</v>
       </c>
       <c r="F28">
-        <v>6.5494</v>
+        <v>6.801300000000001</v>
       </c>
       <c r="G28">
         <v>1.79</v>
@@ -3583,37 +3583,37 @@
         <v>0.828</v>
       </c>
       <c r="M28">
-        <v>0.9614519200000001</v>
+        <v>0.9984308400000003</v>
       </c>
       <c r="N28">
-        <v>-0.1334519200000002</v>
+        <v>-0.1704308400000003</v>
       </c>
       <c r="O28">
-        <v>-0.03603201840000005</v>
+        <v>-0.04601632680000008</v>
       </c>
       <c r="P28">
-        <v>-0.09741990160000012</v>
+        <v>-0.1244145132000002</v>
       </c>
       <c r="Q28">
-        <v>-0.02141990160000005</v>
+        <v>-0.04841451320000015</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1173488233566479</v>
+        <v>0.1183289442245472</v>
       </c>
       <c r="T28">
-        <v>1.3104418266859</v>
+        <v>1.328393084585707</v>
       </c>
       <c r="U28">
         <v>0.1468</v>
       </c>
       <c r="V28">
-        <v>0.2325233278435805</v>
+        <v>0.2239113527382627</v>
       </c>
       <c r="W28">
-        <v>0.1126655754725624</v>
+        <v>0.113929813418023</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>0.8611975105317797</v>
+        <v>0.82930130643801</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1171411789067856</v>
+        <v>0.134187372080577</v>
       </c>
       <c r="C29">
-        <v>12.99453117334977</v>
+        <v>9.27006638031818</v>
       </c>
       <c r="D29">
-        <v>18.00583117334977</v>
+        <v>14.53326638031818</v>
       </c>
       <c r="E29">
-        <v>3.911300000000001</v>
+        <v>4.163200000000002</v>
       </c>
       <c r="F29">
-        <v>6.801300000000001</v>
+        <v>7.053200000000001</v>
       </c>
       <c r="G29">
         <v>1.79</v>
@@ -3665,45 +3665,45 @@
         <v>0.828</v>
       </c>
       <c r="M29">
-        <v>0.9984308400000003</v>
+        <v>1.41628256</v>
       </c>
       <c r="N29">
-        <v>-0.1704308400000003</v>
+        <v>-0.5882825600000002</v>
       </c>
       <c r="O29">
-        <v>-0.04601632680000008</v>
+        <v>-0.1588362912000001</v>
       </c>
       <c r="P29">
-        <v>-0.1244145132000002</v>
+        <v>-0.4294462688000001</v>
       </c>
       <c r="Q29">
-        <v>-0.04841451320000015</v>
+        <v>-0.3534462688000001</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1183289442245472</v>
+        <v>0.120608781191265</v>
       </c>
       <c r="T29">
-        <v>1.328393084585707</v>
+        <v>1.370149099276816</v>
       </c>
       <c r="U29">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V29">
-        <v>0.2239113527382627</v>
+        <v>0.1578498573053106</v>
       </c>
       <c r="W29">
-        <v>0.113929813418023</v>
+        <v>0.1691037486530936</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y29">
-        <v>0.82930130643801</v>
+        <v>0.5846291011307798</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.134187372080577</v>
+        <v>0.135737372080577</v>
       </c>
       <c r="C30">
-        <v>9.27006638031818</v>
+        <v>8.767696943994077</v>
       </c>
       <c r="D30">
-        <v>14.53326638031818</v>
+        <v>14.28279694399408</v>
       </c>
       <c r="E30">
-        <v>4.163200000000002</v>
+        <v>4.415100000000001</v>
       </c>
       <c r="F30">
-        <v>7.053200000000001</v>
+        <v>7.305100000000001</v>
       </c>
       <c r="G30">
         <v>1.79</v>
@@ -3747,37 +3747,37 @@
         <v>0.828</v>
       </c>
       <c r="M30">
-        <v>1.41628256</v>
+        <v>1.46686408</v>
       </c>
       <c r="N30">
-        <v>-0.5882825600000002</v>
+        <v>-0.6388640800000004</v>
       </c>
       <c r="O30">
-        <v>-0.1588362912000001</v>
+        <v>-0.1724933016000001</v>
       </c>
       <c r="P30">
-        <v>-0.4294462688000001</v>
+        <v>-0.4663707784000003</v>
       </c>
       <c r="Q30">
-        <v>-0.3534462688000001</v>
+        <v>-0.3903707784000002</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.120608781191265</v>
+        <v>0.1216624259967758</v>
       </c>
       <c r="T30">
-        <v>1.370149099276816</v>
+        <v>1.389446973914518</v>
       </c>
       <c r="U30">
         <v>0.2008</v>
       </c>
       <c r="V30">
-        <v>0.1578498573053106</v>
+        <v>0.1524067587775412</v>
       </c>
       <c r="W30">
-        <v>0.1691037486530936</v>
+        <v>0.1701967228374697</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>0.5846291011307798</v>
+        <v>0.5644694769538564</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.135737372080577</v>
+        <v>0.137287372080577</v>
       </c>
       <c r="C31">
-        <v>8.767696943994082</v>
+        <v>8.273814528719404</v>
       </c>
       <c r="D31">
-        <v>14.28279694399408</v>
+        <v>14.0408145287194</v>
       </c>
       <c r="E31">
-        <v>4.415099999999999</v>
+        <v>4.667</v>
       </c>
       <c r="F31">
-        <v>7.305099999999999</v>
+        <v>7.557</v>
       </c>
       <c r="G31">
         <v>1.79</v>
@@ -3829,37 +3829,37 @@
         <v>0.828</v>
       </c>
       <c r="M31">
-        <v>1.46686408</v>
+        <v>1.5174456</v>
       </c>
       <c r="N31">
-        <v>-0.6388640799999999</v>
+        <v>-0.6894456000000001</v>
       </c>
       <c r="O31">
-        <v>-0.1724933016</v>
+        <v>-0.186150312</v>
       </c>
       <c r="P31">
-        <v>-0.4663707784</v>
+        <v>-0.5032952880000001</v>
       </c>
       <c r="Q31">
-        <v>-0.3903707783999999</v>
+        <v>-0.4272952880000001</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1216624259967758</v>
+        <v>0.1227461749395869</v>
       </c>
       <c r="T31">
-        <v>1.389446973914518</v>
+        <v>1.409296216399011</v>
       </c>
       <c r="U31">
         <v>0.2008</v>
       </c>
       <c r="V31">
-        <v>0.1524067587775413</v>
+        <v>0.1473265334849566</v>
       </c>
       <c r="W31">
-        <v>0.1701967228374697</v>
+        <v>0.1712168320762207</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>0.5644694769538565</v>
+        <v>0.5456538277220613</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.137287372080577</v>
+        <v>0.138837372080577</v>
       </c>
       <c r="C32">
-        <v>8.273814528719404</v>
+        <v>7.787994953898797</v>
       </c>
       <c r="D32">
-        <v>14.0408145287194</v>
+        <v>13.8068949538988</v>
       </c>
       <c r="E32">
-        <v>4.667</v>
+        <v>4.918900000000001</v>
       </c>
       <c r="F32">
-        <v>7.557</v>
+        <v>7.8089</v>
       </c>
       <c r="G32">
         <v>1.79</v>
@@ -3911,37 +3911,37 @@
         <v>0.828</v>
       </c>
       <c r="M32">
-        <v>1.5174456</v>
+        <v>1.56802712</v>
       </c>
       <c r="N32">
-        <v>-0.6894456000000001</v>
+        <v>-0.7400271200000003</v>
       </c>
       <c r="O32">
-        <v>-0.186150312</v>
+        <v>-0.1998073224000001</v>
       </c>
       <c r="P32">
-        <v>-0.5032952880000001</v>
+        <v>-0.5402197976000002</v>
       </c>
       <c r="Q32">
-        <v>-0.4272952880000001</v>
+        <v>-0.4642197976000001</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1227461749395869</v>
+        <v>0.1238613368952331</v>
       </c>
       <c r="T32">
-        <v>1.409296216399011</v>
+        <v>1.429720799245374</v>
       </c>
       <c r="U32">
         <v>0.2008</v>
       </c>
       <c r="V32">
-        <v>0.1473265334849566</v>
+        <v>0.1425740646628612</v>
       </c>
       <c r="W32">
-        <v>0.1712168320762207</v>
+        <v>0.1721711278156975</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>0.5456538277220613</v>
+        <v>0.5280520913439302</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.138837372080577</v>
+        <v>0.140387372080577</v>
       </c>
       <c r="C33">
-        <v>7.787994953898797</v>
+        <v>7.309841843067971</v>
       </c>
       <c r="D33">
-        <v>13.8068949538988</v>
+        <v>13.58064184306797</v>
       </c>
       <c r="E33">
-        <v>4.918900000000001</v>
+        <v>5.1708</v>
       </c>
       <c r="F33">
-        <v>7.8089</v>
+        <v>8.0608</v>
       </c>
       <c r="G33">
         <v>1.79</v>
@@ -3993,37 +3993,37 @@
         <v>0.828</v>
       </c>
       <c r="M33">
-        <v>1.56802712</v>
+        <v>1.61860864</v>
       </c>
       <c r="N33">
-        <v>-0.7400271200000003</v>
+        <v>-0.7906086400000002</v>
       </c>
       <c r="O33">
-        <v>-0.1998073224000001</v>
+        <v>-0.2134643328000001</v>
       </c>
       <c r="P33">
-        <v>-0.5402197976000002</v>
+        <v>-0.5771443072000001</v>
       </c>
       <c r="Q33">
-        <v>-0.4642197976000001</v>
+        <v>-0.5011443072</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1238613368952331</v>
+        <v>0.1250092977319277</v>
       </c>
       <c r="T33">
-        <v>1.429720799245374</v>
+        <v>1.450746105116629</v>
       </c>
       <c r="U33">
         <v>0.2008</v>
       </c>
       <c r="V33">
-        <v>0.1425740646628612</v>
+        <v>0.1381186251421468</v>
       </c>
       <c r="W33">
-        <v>0.1721711278156975</v>
+        <v>0.1730657800714569</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>0.5280520913439302</v>
+        <v>0.5115504634894324</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.140387372080577</v>
+        <v>0.1538570670925881</v>
       </c>
       <c r="C34">
-        <v>7.309841843067971</v>
+        <v>5.365066877872573</v>
       </c>
       <c r="D34">
-        <v>13.58064184306797</v>
+        <v>11.88776687787257</v>
       </c>
       <c r="E34">
-        <v>5.1708</v>
+        <v>5.422700000000001</v>
       </c>
       <c r="F34">
-        <v>8.0608</v>
+        <v>8.312700000000001</v>
       </c>
       <c r="G34">
         <v>1.79</v>
@@ -4075,45 +4075,45 @@
         <v>0.828</v>
       </c>
       <c r="M34">
-        <v>1.61860864</v>
+        <v>1.96013466</v>
       </c>
       <c r="N34">
-        <v>-0.7906086400000002</v>
+        <v>-1.132134660000001</v>
       </c>
       <c r="O34">
-        <v>-0.2134643328000001</v>
+        <v>-0.3056763582000002</v>
       </c>
       <c r="P34">
-        <v>-0.5771443072000001</v>
+        <v>-0.8264583018000005</v>
       </c>
       <c r="Q34">
-        <v>-0.5011443072</v>
+        <v>-0.7504583018000004</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1250092977319277</v>
+        <v>0.1267433096563014</v>
       </c>
       <c r="T34">
-        <v>1.450746105116629</v>
+        <v>1.482505142471369</v>
       </c>
       <c r="U34">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V34">
-        <v>0.1381186251421468</v>
+        <v>0.114053388556478</v>
       </c>
       <c r="W34">
-        <v>0.1730657800714569</v>
+        <v>0.2089062109783825</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y34">
-        <v>0.5115504634894324</v>
+        <v>0.4224199576165852</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1538570670925881</v>
+        <v>0.1557570670925882</v>
       </c>
       <c r="C35">
-        <v>5.365066877872573</v>
+        <v>4.907752549669917</v>
       </c>
       <c r="D35">
-        <v>11.88776687787257</v>
+        <v>11.68235254966992</v>
       </c>
       <c r="E35">
-        <v>5.422700000000001</v>
+        <v>5.6746</v>
       </c>
       <c r="F35">
-        <v>8.312700000000001</v>
+        <v>8.5646</v>
       </c>
       <c r="G35">
         <v>1.79</v>
@@ -4157,37 +4157,37 @@
         <v>0.828</v>
       </c>
       <c r="M35">
-        <v>1.96013466</v>
+        <v>2.01953268</v>
       </c>
       <c r="N35">
-        <v>-1.132134660000001</v>
+        <v>-1.19153268</v>
       </c>
       <c r="O35">
-        <v>-0.3056763582000002</v>
+        <v>-0.3217138236000001</v>
       </c>
       <c r="P35">
-        <v>-0.8264583018000005</v>
+        <v>-0.8698188564000002</v>
       </c>
       <c r="Q35">
-        <v>-0.7504583018000004</v>
+        <v>-0.7938188564000002</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1267433096563014</v>
+        <v>0.1279697234389726</v>
       </c>
       <c r="T35">
-        <v>1.482505142471369</v>
+        <v>1.504967341599723</v>
       </c>
       <c r="U35">
         <v>0.2358</v>
       </c>
       <c r="V35">
-        <v>0.114053388556478</v>
+        <v>0.1106988771283463</v>
       </c>
       <c r="W35">
-        <v>0.2089062109783825</v>
+        <v>0.2096972047731359</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>0.4224199576165852</v>
+        <v>0.4099958412160974</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1557570670925882</v>
+        <v>0.1576570670925881</v>
       </c>
       <c r="C36">
-        <v>4.907752549669917</v>
+        <v>4.457416541813576</v>
       </c>
       <c r="D36">
-        <v>11.68235254966992</v>
+        <v>11.48391654181358</v>
       </c>
       <c r="E36">
-        <v>5.6746</v>
+        <v>5.926500000000001</v>
       </c>
       <c r="F36">
-        <v>8.5646</v>
+        <v>8.816500000000001</v>
       </c>
       <c r="G36">
         <v>1.79</v>
@@ -4239,37 +4239,37 @@
         <v>0.828</v>
       </c>
       <c r="M36">
-        <v>2.01953268</v>
+        <v>2.0789307</v>
       </c>
       <c r="N36">
-        <v>-1.19153268</v>
+        <v>-1.250930700000001</v>
       </c>
       <c r="O36">
-        <v>-0.3217138236000001</v>
+        <v>-0.3377512890000002</v>
       </c>
       <c r="P36">
-        <v>-0.8698188564000002</v>
+        <v>-0.9131794110000003</v>
       </c>
       <c r="Q36">
-        <v>-0.7938188564000002</v>
+        <v>-0.8371794110000003</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1279697234389726</v>
+        <v>0.1292338730303415</v>
       </c>
       <c r="T36">
-        <v>1.504967341599723</v>
+        <v>1.528120685316642</v>
       </c>
       <c r="U36">
         <v>0.2358</v>
       </c>
       <c r="V36">
-        <v>0.1106988771283463</v>
+        <v>0.1075360520675364</v>
       </c>
       <c r="W36">
-        <v>0.2096972047731359</v>
+        <v>0.2104429989224749</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>0.4099958412160974</v>
+        <v>0.3982816743242089</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1576570670925881</v>
+        <v>0.1595570670925882</v>
       </c>
       <c r="C37">
-        <v>4.457416541813576</v>
+        <v>4.013709193161668</v>
       </c>
       <c r="D37">
-        <v>11.48391654181358</v>
+        <v>11.29210919316167</v>
       </c>
       <c r="E37">
-        <v>5.926500000000001</v>
+        <v>6.178400000000002</v>
       </c>
       <c r="F37">
-        <v>8.816500000000001</v>
+        <v>9.068400000000002</v>
       </c>
       <c r="G37">
         <v>1.79</v>
@@ -4321,37 +4321,37 @@
         <v>0.828</v>
       </c>
       <c r="M37">
-        <v>2.0789307</v>
+        <v>2.138328720000001</v>
       </c>
       <c r="N37">
-        <v>-1.250930700000001</v>
+        <v>-1.310328720000001</v>
       </c>
       <c r="O37">
-        <v>-0.3377512890000002</v>
+        <v>-0.3537887544000002</v>
       </c>
       <c r="P37">
-        <v>-0.9131794110000003</v>
+        <v>-0.9565399656000004</v>
       </c>
       <c r="Q37">
-        <v>-0.8371794110000003</v>
+        <v>-0.8805399656000004</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1292338730303415</v>
+        <v>0.1305375272964406</v>
       </c>
       <c r="T37">
-        <v>1.528120685316642</v>
+        <v>1.551997571024714</v>
       </c>
       <c r="U37">
         <v>0.2358</v>
       </c>
       <c r="V37">
-        <v>0.1075360520675364</v>
+        <v>0.1045489395101049</v>
       </c>
       <c r="W37">
-        <v>0.2104429989224749</v>
+        <v>0.2111473600635173</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>0.3982816743242089</v>
+        <v>0.3872182944818697</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1595570670925882</v>
+        <v>0.1614570670925882</v>
       </c>
       <c r="C38">
-        <v>4.01370919316167</v>
+        <v>3.576303819332406</v>
       </c>
       <c r="D38">
-        <v>11.29210919316167</v>
+        <v>11.1066038193324</v>
       </c>
       <c r="E38">
-        <v>6.1784</v>
+        <v>6.430299999999999</v>
       </c>
       <c r="F38">
-        <v>9.0684</v>
+        <v>9.3203</v>
       </c>
       <c r="G38">
         <v>1.79</v>
@@ -4403,37 +4403,37 @@
         <v>0.828</v>
       </c>
       <c r="M38">
-        <v>2.13832872</v>
+        <v>2.19772674</v>
       </c>
       <c r="N38">
-        <v>-1.31032872</v>
+        <v>-1.36972674</v>
       </c>
       <c r="O38">
-        <v>-0.3537887544000001</v>
+        <v>-0.3698262198</v>
       </c>
       <c r="P38">
-        <v>-0.9565399656000002</v>
+        <v>-0.9999005202</v>
       </c>
       <c r="Q38">
-        <v>-0.8805399656000001</v>
+        <v>-0.9239005201999999</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1305375272964405</v>
+        <v>0.131882567412257</v>
       </c>
       <c r="T38">
-        <v>1.551997571024714</v>
+        <v>1.576632453104472</v>
       </c>
       <c r="U38">
         <v>0.2358</v>
       </c>
       <c r="V38">
-        <v>0.1045489395101049</v>
+        <v>0.1017232924963183</v>
       </c>
       <c r="W38">
-        <v>0.2111473600635173</v>
+        <v>0.2118136476293682</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>0.3872182944818698</v>
+        <v>0.3767529351715491</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1614570670925882</v>
+        <v>0.1633570670925882</v>
       </c>
       <c r="C39">
-        <v>3.576303819332406</v>
+        <v>3.14489485591031</v>
       </c>
       <c r="D39">
-        <v>11.1066038193324</v>
+        <v>10.92709485591031</v>
       </c>
       <c r="E39">
-        <v>6.430299999999999</v>
+        <v>6.6822</v>
       </c>
       <c r="F39">
-        <v>9.3203</v>
+        <v>9.5722</v>
       </c>
       <c r="G39">
         <v>1.79</v>
@@ -4485,37 +4485,37 @@
         <v>0.828</v>
       </c>
       <c r="M39">
-        <v>2.19772674</v>
+        <v>2.25712476</v>
       </c>
       <c r="N39">
-        <v>-1.36972674</v>
+        <v>-1.429124760000001</v>
       </c>
       <c r="O39">
-        <v>-0.3698262198</v>
+        <v>-0.3858636852000002</v>
       </c>
       <c r="P39">
-        <v>-0.9999005202</v>
+        <v>-1.0432610748</v>
       </c>
       <c r="Q39">
-        <v>-0.9239005201999999</v>
+        <v>-0.9672610748000003</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.131882567412257</v>
+        <v>0.1332709959189064</v>
       </c>
       <c r="T39">
-        <v>1.576632453104472</v>
+        <v>1.602062008799705</v>
       </c>
       <c r="U39">
         <v>0.2358</v>
       </c>
       <c r="V39">
-        <v>0.1017232924963183</v>
+        <v>0.09904636374641514</v>
       </c>
       <c r="W39">
-        <v>0.2118136476293682</v>
+        <v>0.2124448674285953</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.3767529351715491</v>
+        <v>0.3668383842459819</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1633570670925882</v>
+        <v>0.1652570670925882</v>
       </c>
       <c r="C40">
-        <v>3.14489485591031</v>
+        <v>2.719196178849725</v>
       </c>
       <c r="D40">
-        <v>10.92709485591031</v>
+        <v>10.75329617884973</v>
       </c>
       <c r="E40">
-        <v>6.6822</v>
+        <v>6.934100000000001</v>
       </c>
       <c r="F40">
-        <v>9.5722</v>
+        <v>9.824100000000001</v>
       </c>
       <c r="G40">
         <v>1.79</v>
@@ -4567,37 +4567,37 @@
         <v>0.828</v>
       </c>
       <c r="M40">
-        <v>2.25712476</v>
+        <v>2.316522780000001</v>
       </c>
       <c r="N40">
-        <v>-1.429124760000001</v>
+        <v>-1.488522780000001</v>
       </c>
       <c r="O40">
-        <v>-0.3858636852000002</v>
+        <v>-0.4019011506000002</v>
       </c>
       <c r="P40">
-        <v>-1.0432610748</v>
+        <v>-1.086621629400001</v>
       </c>
       <c r="Q40">
-        <v>-0.9672610748000003</v>
+        <v>-1.010621629400001</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1332709959189064</v>
+        <v>0.1347049466716753</v>
       </c>
       <c r="T40">
-        <v>1.602062008799705</v>
+        <v>1.628325320419372</v>
       </c>
       <c r="U40">
         <v>0.2358</v>
       </c>
       <c r="V40">
-        <v>0.09904636374641514</v>
+        <v>0.09650671339394294</v>
       </c>
       <c r="W40">
-        <v>0.2124448674285953</v>
+        <v>0.2130437169817083</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.3668383842459819</v>
+        <v>0.3574322718294183</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1652570670925882</v>
+        <v>0.1671570670925882</v>
       </c>
       <c r="C41">
-        <v>2.719196178849725</v>
+        <v>2.298939582655567</v>
       </c>
       <c r="D41">
-        <v>10.75329617884973</v>
+        <v>10.58493958265557</v>
       </c>
       <c r="E41">
-        <v>6.934100000000001</v>
+        <v>7.186</v>
       </c>
       <c r="F41">
-        <v>9.824100000000001</v>
+        <v>10.076</v>
       </c>
       <c r="G41">
         <v>1.79</v>
@@ -4649,37 +4649,37 @@
         <v>0.828</v>
       </c>
       <c r="M41">
-        <v>2.316522780000001</v>
+        <v>2.3759208</v>
       </c>
       <c r="N41">
-        <v>-1.488522780000001</v>
+        <v>-1.5479208</v>
       </c>
       <c r="O41">
-        <v>-0.4019011506000002</v>
+        <v>-0.4179386160000002</v>
       </c>
       <c r="P41">
-        <v>-1.086621629400001</v>
+        <v>-1.129982184</v>
       </c>
       <c r="Q41">
-        <v>-1.010621629400001</v>
+        <v>-1.053982184</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1347049466716753</v>
+        <v>0.1361866957828699</v>
       </c>
       <c r="T41">
-        <v>1.628325320419372</v>
+        <v>1.655464075759695</v>
       </c>
       <c r="U41">
         <v>0.2358</v>
       </c>
       <c r="V41">
-        <v>0.09650671339394294</v>
+        <v>0.09409404555909438</v>
       </c>
       <c r="W41">
-        <v>0.2130437169817083</v>
+        <v>0.2136126240571656</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.3574322718294183</v>
+        <v>0.3484964650336828</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1671570670925882</v>
+        <v>0.1690570670925882</v>
       </c>
       <c r="C42">
-        <v>2.298939582655567</v>
+        <v>1.883873399316654</v>
       </c>
       <c r="D42">
-        <v>10.58493958265557</v>
+        <v>10.42177339931666</v>
       </c>
       <c r="E42">
-        <v>7.186</v>
+        <v>7.437900000000001</v>
       </c>
       <c r="F42">
-        <v>10.076</v>
+        <v>10.3279</v>
       </c>
       <c r="G42">
         <v>1.79</v>
@@ -4731,37 +4731,37 @@
         <v>0.828</v>
       </c>
       <c r="M42">
-        <v>2.3759208</v>
+        <v>2.43531882</v>
       </c>
       <c r="N42">
-        <v>-1.5479208</v>
+        <v>-1.607318820000001</v>
       </c>
       <c r="O42">
-        <v>-0.4179386160000002</v>
+        <v>-0.4339760814000002</v>
       </c>
       <c r="P42">
-        <v>-1.129982184</v>
+        <v>-1.1733427386</v>
       </c>
       <c r="Q42">
-        <v>-1.053982184</v>
+        <v>-1.0973427386</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1361866957828699</v>
+        <v>0.1377186736774948</v>
       </c>
       <c r="T42">
-        <v>1.655464075759695</v>
+        <v>1.683522788908165</v>
       </c>
       <c r="U42">
         <v>0.2358</v>
       </c>
       <c r="V42">
-        <v>0.09409404555909438</v>
+        <v>0.09179906883814086</v>
       </c>
       <c r="W42">
-        <v>0.2136126240571656</v>
+        <v>0.2141537795679664</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.3484964650336828</v>
+        <v>0.3399965512523735</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1690570670925882</v>
+        <v>0.1709570670925882</v>
       </c>
       <c r="C43">
-        <v>1.883873399316654</v>
+        <v>1.473761243034236</v>
       </c>
       <c r="D43">
-        <v>10.42177339931666</v>
+        <v>10.26356124303424</v>
       </c>
       <c r="E43">
-        <v>7.437900000000001</v>
+        <v>7.689800000000002</v>
       </c>
       <c r="F43">
-        <v>10.3279</v>
+        <v>10.5798</v>
       </c>
       <c r="G43">
         <v>1.79</v>
@@ -4813,37 +4813,37 @@
         <v>0.828</v>
       </c>
       <c r="M43">
-        <v>2.43531882</v>
+        <v>2.494716840000001</v>
       </c>
       <c r="N43">
-        <v>-1.607318820000001</v>
+        <v>-1.666716840000001</v>
       </c>
       <c r="O43">
-        <v>-0.4339760814000002</v>
+        <v>-0.4500135468000002</v>
       </c>
       <c r="P43">
-        <v>-1.1733427386</v>
+        <v>-1.216703293200001</v>
       </c>
       <c r="Q43">
-        <v>-1.0973427386</v>
+        <v>-1.140703293200001</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1377186736774948</v>
+        <v>0.1393034783960723</v>
       </c>
       <c r="T43">
-        <v>1.683522788908165</v>
+        <v>1.71254904388934</v>
       </c>
       <c r="U43">
         <v>0.2358</v>
       </c>
       <c r="V43">
-        <v>0.09179906883814086</v>
+        <v>0.08961337672294703</v>
       </c>
       <c r="W43">
-        <v>0.2141537795679664</v>
+        <v>0.2146691657687291</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.3399965512523735</v>
+        <v>0.331901395270174</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1709570670925882</v>
+        <v>0.1728570670925882</v>
       </c>
       <c r="C44">
-        <v>1.473761243034238</v>
+        <v>1.068380867577792</v>
       </c>
       <c r="D44">
-        <v>10.26356124303424</v>
+        <v>10.11008086757779</v>
       </c>
       <c r="E44">
-        <v>7.6898</v>
+        <v>7.941699999999999</v>
       </c>
       <c r="F44">
-        <v>10.5798</v>
+        <v>10.8317</v>
       </c>
       <c r="G44">
         <v>1.79</v>
@@ -4895,37 +4895,37 @@
         <v>0.828</v>
       </c>
       <c r="M44">
-        <v>2.49471684</v>
+        <v>2.55411486</v>
       </c>
       <c r="N44">
-        <v>-1.66671684</v>
+        <v>-1.72611486</v>
       </c>
       <c r="O44">
-        <v>-0.4500135468000001</v>
+        <v>-0.4660510122000001</v>
       </c>
       <c r="P44">
-        <v>-1.2167032932</v>
+        <v>-1.2600638478</v>
       </c>
       <c r="Q44">
-        <v>-1.1407032932</v>
+        <v>-1.1840638478</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1393034783960723</v>
+        <v>0.1409438902977578</v>
       </c>
       <c r="T44">
-        <v>1.71254904388934</v>
+        <v>1.742593763957574</v>
       </c>
       <c r="U44">
         <v>0.2358</v>
       </c>
       <c r="V44">
-        <v>0.08961337672294704</v>
+        <v>0.08752934470613433</v>
       </c>
       <c r="W44">
-        <v>0.2146691657687291</v>
+        <v>0.2151605805182935</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.3319013952701741</v>
+        <v>0.3241827581708678</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1728570670925882</v>
+        <v>0.1747570670925882</v>
       </c>
       <c r="C45">
-        <v>1.068380867577792</v>
+        <v>0.667523124652341</v>
       </c>
       <c r="D45">
-        <v>10.11008086757779</v>
+        <v>9.961123124652342</v>
       </c>
       <c r="E45">
-        <v>7.941699999999999</v>
+        <v>8.1936</v>
       </c>
       <c r="F45">
-        <v>10.8317</v>
+        <v>11.0836</v>
       </c>
       <c r="G45">
         <v>1.79</v>
@@ -4977,37 +4977,37 @@
         <v>0.828</v>
       </c>
       <c r="M45">
-        <v>2.55411486</v>
+        <v>2.61351288</v>
       </c>
       <c r="N45">
-        <v>-1.72611486</v>
+        <v>-1.78551288</v>
       </c>
       <c r="O45">
-        <v>-0.4660510122000001</v>
+        <v>-0.4820884776000001</v>
       </c>
       <c r="P45">
-        <v>-1.2600638478</v>
+        <v>-1.3034244024</v>
       </c>
       <c r="Q45">
-        <v>-1.1840638478</v>
+        <v>-1.2274244024</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1409438902977578</v>
+        <v>0.1426428883387892</v>
       </c>
       <c r="T45">
-        <v>1.742593763957574</v>
+        <v>1.773711509742531</v>
       </c>
       <c r="U45">
         <v>0.2358</v>
       </c>
       <c r="V45">
-        <v>0.08752934470613433</v>
+        <v>0.08554004141735855</v>
       </c>
       <c r="W45">
-        <v>0.2151605805182935</v>
+        <v>0.2156296582337869</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.3241827581708678</v>
+        <v>0.3168149682124389</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1747570670925882</v>
+        <v>0.1766570670925882</v>
       </c>
       <c r="C46">
-        <v>0.667523124652341</v>
+        <v>0.2709910130106525</v>
       </c>
       <c r="D46">
-        <v>9.961123124652342</v>
+        <v>9.816491013010653</v>
       </c>
       <c r="E46">
-        <v>8.1936</v>
+        <v>8.445500000000001</v>
       </c>
       <c r="F46">
-        <v>11.0836</v>
+        <v>11.3355</v>
       </c>
       <c r="G46">
         <v>1.79</v>
@@ -5059,37 +5059,37 @@
         <v>0.828</v>
       </c>
       <c r="M46">
-        <v>2.61351288</v>
+        <v>2.672910900000001</v>
       </c>
       <c r="N46">
-        <v>-1.78551288</v>
+        <v>-1.844910900000001</v>
       </c>
       <c r="O46">
-        <v>-0.4820884776000001</v>
+        <v>-0.4981259430000002</v>
       </c>
       <c r="P46">
-        <v>-1.3034244024</v>
+        <v>-1.346784957000001</v>
       </c>
       <c r="Q46">
-        <v>-1.2274244024</v>
+        <v>-1.270784957</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1426428883387892</v>
+        <v>0.1444036681267672</v>
       </c>
       <c r="T46">
-        <v>1.773711509742531</v>
+        <v>1.805960809919668</v>
       </c>
       <c r="U46">
         <v>0.2358</v>
       </c>
       <c r="V46">
-        <v>0.08554004141735855</v>
+        <v>0.08363915160808388</v>
       </c>
       <c r="W46">
-        <v>0.2156296582337869</v>
+        <v>0.2160778880508138</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.3168149682124389</v>
+        <v>0.3097746355854958</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1766570670925882</v>
+        <v>0.1785570670925882</v>
       </c>
       <c r="C47">
-        <v>0.2709910130106525</v>
+        <v>-0.1214011907807464</v>
       </c>
       <c r="D47">
-        <v>9.816491013010653</v>
+        <v>9.675998809219255</v>
       </c>
       <c r="E47">
-        <v>8.445500000000001</v>
+        <v>8.6974</v>
       </c>
       <c r="F47">
-        <v>11.3355</v>
+        <v>11.5874</v>
       </c>
       <c r="G47">
         <v>1.79</v>
@@ -5141,37 +5141,37 @@
         <v>0.828</v>
       </c>
       <c r="M47">
-        <v>2.672910900000001</v>
+        <v>2.73230892</v>
       </c>
       <c r="N47">
-        <v>-1.844910900000001</v>
+        <v>-1.904308920000001</v>
       </c>
       <c r="O47">
-        <v>-0.4981259430000002</v>
+        <v>-0.5141634084000002</v>
       </c>
       <c r="P47">
-        <v>-1.346784957000001</v>
+        <v>-1.3901455116</v>
       </c>
       <c r="Q47">
-        <v>-1.270784957</v>
+        <v>-1.3141455116</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1444036681267672</v>
+        <v>0.1462296619809666</v>
       </c>
       <c r="T47">
-        <v>1.805960809919668</v>
+        <v>1.839404528621884</v>
       </c>
       <c r="U47">
         <v>0.2358</v>
       </c>
       <c r="V47">
-        <v>0.08363915160808388</v>
+        <v>0.08182090918182121</v>
       </c>
       <c r="W47">
-        <v>0.2160778880508138</v>
+        <v>0.2165066296149266</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.3097746355854958</v>
+        <v>0.3030404043771155</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1785570670925882</v>
+        <v>0.1804570670925882</v>
       </c>
       <c r="C48">
-        <v>-0.1214011907807464</v>
+        <v>-0.5098287279866192</v>
       </c>
       <c r="D48">
-        <v>9.675998809219255</v>
+        <v>9.539471272013383</v>
       </c>
       <c r="E48">
-        <v>8.6974</v>
+        <v>8.949300000000001</v>
       </c>
       <c r="F48">
-        <v>11.5874</v>
+        <v>11.8393</v>
       </c>
       <c r="G48">
         <v>1.79</v>
@@ -5223,37 +5223,37 @@
         <v>0.828</v>
       </c>
       <c r="M48">
-        <v>2.73230892</v>
+        <v>2.791706940000001</v>
       </c>
       <c r="N48">
-        <v>-1.904308920000001</v>
+        <v>-1.963706940000001</v>
       </c>
       <c r="O48">
-        <v>-0.5141634084000002</v>
+        <v>-0.5302008738000002</v>
       </c>
       <c r="P48">
-        <v>-1.3901455116</v>
+        <v>-1.433506066200001</v>
       </c>
       <c r="Q48">
-        <v>-1.3141455116</v>
+        <v>-1.3575060662</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1462296619809666</v>
+        <v>0.1481245612636263</v>
       </c>
       <c r="T48">
-        <v>1.839404528621884</v>
+        <v>1.874110274444938</v>
       </c>
       <c r="U48">
         <v>0.2358</v>
       </c>
       <c r="V48">
-        <v>0.08182090918182121</v>
+        <v>0.08008003877369735</v>
       </c>
       <c r="W48">
-        <v>0.2165066296149266</v>
+        <v>0.2169171268571622</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.3030404043771155</v>
+        <v>0.2965927361988789</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1804570670925882</v>
+        <v>0.1823570670925882</v>
       </c>
       <c r="C49">
-        <v>-0.5098287279866192</v>
+        <v>-0.894457086926371</v>
       </c>
       <c r="D49">
-        <v>9.539471272013383</v>
+        <v>9.40674291307363</v>
       </c>
       <c r="E49">
-        <v>8.949300000000001</v>
+        <v>9.201200000000002</v>
       </c>
       <c r="F49">
-        <v>11.8393</v>
+        <v>12.0912</v>
       </c>
       <c r="G49">
         <v>1.79</v>
@@ -5305,37 +5305,37 @@
         <v>0.828</v>
       </c>
       <c r="M49">
-        <v>2.791706940000001</v>
+        <v>2.851104960000001</v>
       </c>
       <c r="N49">
-        <v>-1.963706940000001</v>
+        <v>-2.023104960000001</v>
       </c>
       <c r="O49">
-        <v>-0.5302008738000002</v>
+        <v>-0.5462383392000003</v>
       </c>
       <c r="P49">
-        <v>-1.433506066200001</v>
+        <v>-1.476866620800001</v>
       </c>
       <c r="Q49">
-        <v>-1.3575060662</v>
+        <v>-1.4008666208</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1481245612636263</v>
+        <v>0.1500923412879268</v>
       </c>
       <c r="T49">
-        <v>1.874110274444938</v>
+        <v>1.910150856645802</v>
       </c>
       <c r="U49">
         <v>0.2358</v>
       </c>
       <c r="V49">
-        <v>0.08008003877369735</v>
+        <v>0.07841170463257864</v>
       </c>
       <c r="W49">
-        <v>0.2169171268571622</v>
+        <v>0.217310520047638</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.2965927361988789</v>
+        <v>0.2904137208614024</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1823570670925881</v>
+        <v>0.1842570670925882</v>
       </c>
       <c r="C50">
-        <v>-0.8944570869263693</v>
+        <v>-1.275442672156107</v>
       </c>
       <c r="D50">
-        <v>9.40674291307363</v>
+        <v>9.277657327843892</v>
       </c>
       <c r="E50">
-        <v>9.2012</v>
+        <v>9.453099999999999</v>
       </c>
       <c r="F50">
-        <v>12.0912</v>
+        <v>12.3431</v>
       </c>
       <c r="G50">
         <v>1.79</v>
@@ -5387,37 +5387,37 @@
         <v>0.828</v>
       </c>
       <c r="M50">
-        <v>2.85110496</v>
+        <v>2.91050298</v>
       </c>
       <c r="N50">
-        <v>-2.02310496</v>
+        <v>-2.08250298</v>
       </c>
       <c r="O50">
-        <v>-0.5462383392000001</v>
+        <v>-0.5622758046</v>
       </c>
       <c r="P50">
-        <v>-1.4768666208</v>
+        <v>-1.5202271754</v>
       </c>
       <c r="Q50">
-        <v>-1.4008666208</v>
+        <v>-1.4442271754</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1500923412879268</v>
+        <v>0.1521372891563175</v>
       </c>
       <c r="T50">
-        <v>1.910150856645802</v>
+        <v>1.947604795011406</v>
       </c>
       <c r="U50">
         <v>0.2358</v>
       </c>
       <c r="V50">
-        <v>0.07841170463257867</v>
+        <v>0.07681146576252604</v>
       </c>
       <c r="W50">
-        <v>0.217310520047638</v>
+        <v>0.2176878563731964</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.2904137208614024</v>
+        <v>0.2844869102315779</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1842570670925882</v>
+        <v>0.1861570670925882</v>
       </c>
       <c r="C51">
-        <v>-1.275442672156107</v>
+        <v>-1.652933419298718</v>
       </c>
       <c r="D51">
-        <v>9.277657327843892</v>
+        <v>9.152066580701282</v>
       </c>
       <c r="E51">
-        <v>9.453099999999999</v>
+        <v>9.705</v>
       </c>
       <c r="F51">
-        <v>12.3431</v>
+        <v>12.595</v>
       </c>
       <c r="G51">
         <v>1.79</v>
@@ -5469,37 +5469,37 @@
         <v>0.828</v>
       </c>
       <c r="M51">
-        <v>2.91050298</v>
+        <v>2.969901</v>
       </c>
       <c r="N51">
-        <v>-2.08250298</v>
+        <v>-2.141901</v>
       </c>
       <c r="O51">
-        <v>-0.5622758046</v>
+        <v>-0.5783132700000001</v>
       </c>
       <c r="P51">
-        <v>-1.5202271754</v>
+        <v>-1.56358773</v>
       </c>
       <c r="Q51">
-        <v>-1.4442271754</v>
+        <v>-1.48758773</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1521372891563175</v>
+        <v>0.1542640349394439</v>
       </c>
       <c r="T51">
-        <v>1.947604795011406</v>
+        <v>1.986556890911634</v>
       </c>
       <c r="U51">
         <v>0.2358</v>
       </c>
       <c r="V51">
-        <v>0.07681146576252604</v>
+        <v>0.0752752364472755</v>
       </c>
       <c r="W51">
-        <v>0.2176878563731964</v>
+        <v>0.2180500992457324</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.2844869102315779</v>
+        <v>0.2787971720269463</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1861570670925882</v>
+        <v>0.1880570670925882</v>
       </c>
       <c r="C52">
-        <v>-1.652933419298718</v>
+        <v>-2.027069360603591</v>
       </c>
       <c r="D52">
-        <v>9.152066580701282</v>
+        <v>9.029830639396412</v>
       </c>
       <c r="E52">
-        <v>9.705</v>
+        <v>9.956900000000001</v>
       </c>
       <c r="F52">
-        <v>12.595</v>
+        <v>12.8469</v>
       </c>
       <c r="G52">
         <v>1.79</v>
@@ -5551,37 +5551,37 @@
         <v>0.828</v>
       </c>
       <c r="M52">
-        <v>2.969901</v>
+        <v>3.02929902</v>
       </c>
       <c r="N52">
-        <v>-2.141901</v>
+        <v>-2.20129902</v>
       </c>
       <c r="O52">
-        <v>-0.5783132700000001</v>
+        <v>-0.5943507354000002</v>
       </c>
       <c r="P52">
-        <v>-1.56358773</v>
+        <v>-1.6069482846</v>
       </c>
       <c r="Q52">
-        <v>-1.48758773</v>
+        <v>-1.5309482846</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1542640349394439</v>
+        <v>0.1564775866729019</v>
       </c>
       <c r="T52">
-        <v>1.986556890911634</v>
+        <v>2.027098868277178</v>
       </c>
       <c r="U52">
         <v>0.2358</v>
       </c>
       <c r="V52">
-        <v>0.0752752364472755</v>
+        <v>0.07379925141889757</v>
       </c>
       <c r="W52">
-        <v>0.2180500992457324</v>
+        <v>0.218398136515424</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.2787971720269463</v>
+        <v>0.2733305608107316</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1880570670925882</v>
+        <v>0.1899570670925882</v>
       </c>
       <c r="C53">
-        <v>-2.027069360603591</v>
+        <v>-2.397983145781627</v>
       </c>
       <c r="D53">
-        <v>9.029830639396412</v>
+        <v>8.910816854218373</v>
       </c>
       <c r="E53">
-        <v>9.956900000000001</v>
+        <v>10.2088</v>
       </c>
       <c r="F53">
-        <v>12.8469</v>
+        <v>13.0988</v>
       </c>
       <c r="G53">
         <v>1.79</v>
@@ -5633,37 +5633,37 @@
         <v>0.828</v>
       </c>
       <c r="M53">
-        <v>3.02929902</v>
+        <v>3.08869704</v>
       </c>
       <c r="N53">
-        <v>-2.20129902</v>
+        <v>-2.260697040000001</v>
       </c>
       <c r="O53">
-        <v>-0.5943507354000002</v>
+        <v>-0.6103882008000002</v>
       </c>
       <c r="P53">
-        <v>-1.6069482846</v>
+        <v>-1.6503088392</v>
       </c>
       <c r="Q53">
-        <v>-1.5309482846</v>
+        <v>-1.5743088392</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1564775866729019</v>
+        <v>0.1587833697285874</v>
       </c>
       <c r="T53">
-        <v>2.027098868277178</v>
+        <v>2.06933009469962</v>
       </c>
       <c r="U53">
         <v>0.2358</v>
       </c>
       <c r="V53">
-        <v>0.07379925141889757</v>
+        <v>0.07238003504545722</v>
       </c>
       <c r="W53">
-        <v>0.218398136515424</v>
+        <v>0.2187327877362812</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.2733305608107316</v>
+        <v>0.2680742038720637</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1899570670925882</v>
+        <v>0.1918570670925882</v>
       </c>
       <c r="C54">
-        <v>-2.397983145781627</v>
+        <v>-2.765800522188224</v>
       </c>
       <c r="D54">
-        <v>8.910816854218373</v>
+        <v>8.794899477811779</v>
       </c>
       <c r="E54">
-        <v>10.2088</v>
+        <v>10.4607</v>
       </c>
       <c r="F54">
-        <v>13.0988</v>
+        <v>13.3507</v>
       </c>
       <c r="G54">
         <v>1.79</v>
@@ -5715,37 +5715,37 @@
         <v>0.828</v>
       </c>
       <c r="M54">
-        <v>3.08869704</v>
+        <v>3.148095060000001</v>
       </c>
       <c r="N54">
-        <v>-2.260697040000001</v>
+        <v>-2.320095060000001</v>
       </c>
       <c r="O54">
-        <v>-0.6103882008000002</v>
+        <v>-0.6264256662000003</v>
       </c>
       <c r="P54">
-        <v>-1.6503088392</v>
+        <v>-1.6936693938</v>
       </c>
       <c r="Q54">
-        <v>-1.5743088392</v>
+        <v>-1.6176693938</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1587833697285874</v>
+        <v>0.1611872712121744</v>
       </c>
       <c r="T54">
-        <v>2.06933009469962</v>
+        <v>2.113358394586846</v>
       </c>
       <c r="U54">
         <v>0.2358</v>
       </c>
       <c r="V54">
-        <v>0.07238003504545722</v>
+        <v>0.07101437400686368</v>
       </c>
       <c r="W54">
-        <v>0.2187327877362812</v>
+        <v>0.2190548106091816</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.2680742038720637</v>
+        <v>0.263016200025421</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1918570670925882</v>
+        <v>0.1937570670925882</v>
       </c>
       <c r="C55">
-        <v>-2.765800522188224</v>
+        <v>-3.130640778008416</v>
       </c>
       <c r="D55">
-        <v>8.794899477811779</v>
+        <v>8.681959221991587</v>
       </c>
       <c r="E55">
-        <v>10.4607</v>
+        <v>10.7126</v>
       </c>
       <c r="F55">
-        <v>13.3507</v>
+        <v>13.6026</v>
       </c>
       <c r="G55">
         <v>1.79</v>
@@ -5797,37 +5797,37 @@
         <v>0.828</v>
       </c>
       <c r="M55">
-        <v>3.148095060000001</v>
+        <v>3.207493080000001</v>
       </c>
       <c r="N55">
-        <v>-2.320095060000001</v>
+        <v>-2.379493080000001</v>
       </c>
       <c r="O55">
-        <v>-0.6264256662000003</v>
+        <v>-0.6424631316000003</v>
       </c>
       <c r="P55">
-        <v>-1.6936693938</v>
+        <v>-1.7370299484</v>
       </c>
       <c r="Q55">
-        <v>-1.6176693938</v>
+        <v>-1.6610299484</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1611872712121744</v>
+        <v>0.1636956901515695</v>
       </c>
       <c r="T55">
-        <v>2.113358394586846</v>
+        <v>2.159300968382211</v>
       </c>
       <c r="U55">
         <v>0.2358</v>
       </c>
       <c r="V55">
-        <v>0.07101437400686368</v>
+        <v>0.06969929300673657</v>
       </c>
       <c r="W55">
-        <v>0.2190548106091816</v>
+        <v>0.2193649067090115</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.263016200025421</v>
+        <v>0.2581455296545798</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1937570670925882</v>
+        <v>0.1956570670925882</v>
       </c>
       <c r="C56">
-        <v>-3.130640778008416</v>
+        <v>-3.492617151727863</v>
       </c>
       <c r="D56">
-        <v>8.681959221991587</v>
+        <v>8.571882848272139</v>
       </c>
       <c r="E56">
-        <v>10.7126</v>
+        <v>10.9645</v>
       </c>
       <c r="F56">
-        <v>13.6026</v>
+        <v>13.8545</v>
       </c>
       <c r="G56">
         <v>1.79</v>
@@ -5879,37 +5879,37 @@
         <v>0.828</v>
       </c>
       <c r="M56">
-        <v>3.207493080000001</v>
+        <v>3.2668911</v>
       </c>
       <c r="N56">
-        <v>-2.379493080000001</v>
+        <v>-2.438891100000001</v>
       </c>
       <c r="O56">
-        <v>-0.6424631316000003</v>
+        <v>-0.6585005970000002</v>
       </c>
       <c r="P56">
-        <v>-1.7370299484</v>
+        <v>-1.780390503</v>
       </c>
       <c r="Q56">
-        <v>-1.6610299484</v>
+        <v>-1.704390503</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1636956901515695</v>
+        <v>0.1663155943771599</v>
       </c>
       <c r="T56">
-        <v>2.159300968382211</v>
+        <v>2.207285434346261</v>
       </c>
       <c r="U56">
         <v>0.2358</v>
       </c>
       <c r="V56">
-        <v>0.06969929300673657</v>
+        <v>0.06843203313388682</v>
       </c>
       <c r="W56">
-        <v>0.2193649067090115</v>
+        <v>0.2196637265870295</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.2581455296545798</v>
+        <v>0.2534519745699512</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1956570670925882</v>
+        <v>0.1975570670925882</v>
       </c>
       <c r="C57">
-        <v>-3.492617151727863</v>
+        <v>-3.851837210844321</v>
       </c>
       <c r="D57">
-        <v>8.571882848272139</v>
+        <v>8.46456278915568</v>
       </c>
       <c r="E57">
-        <v>10.9645</v>
+        <v>11.2164</v>
       </c>
       <c r="F57">
-        <v>13.8545</v>
+        <v>14.1064</v>
       </c>
       <c r="G57">
         <v>1.79</v>
@@ -5961,37 +5961,37 @@
         <v>0.828</v>
       </c>
       <c r="M57">
-        <v>3.2668911</v>
+        <v>3.326289120000001</v>
       </c>
       <c r="N57">
-        <v>-2.438891100000001</v>
+        <v>-2.498289120000001</v>
       </c>
       <c r="O57">
-        <v>-0.6585005970000002</v>
+        <v>-0.6745380624000002</v>
       </c>
       <c r="P57">
-        <v>-1.780390503</v>
+        <v>-1.8237510576</v>
       </c>
       <c r="Q57">
-        <v>-1.704390503</v>
+        <v>-1.7477510576</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1663155943771599</v>
+        <v>0.169054585158459</v>
       </c>
       <c r="T57">
-        <v>2.207285434346261</v>
+        <v>2.257451012399585</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>0.06843203313388682</v>
+        <v>0.06721003254221027</v>
       </c>
       <c r="W57">
-        <v>0.2196637265870295</v>
+        <v>0.2199518743265468</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.2534519745699512</v>
+        <v>0.2489260464526306</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1975570670925882</v>
+        <v>0.1994570670925882</v>
       </c>
       <c r="C58">
-        <v>-3.851837210844321</v>
+        <v>-4.208403202482083</v>
       </c>
       <c r="D58">
-        <v>8.46456278915568</v>
+        <v>8.359896797517917</v>
       </c>
       <c r="E58">
-        <v>11.2164</v>
+        <v>11.4683</v>
       </c>
       <c r="F58">
-        <v>14.1064</v>
+        <v>14.3583</v>
       </c>
       <c r="G58">
         <v>1.79</v>
@@ -6043,37 +6043,37 @@
         <v>0.828</v>
       </c>
       <c r="M58">
-        <v>3.326289120000001</v>
+        <v>3.38568714</v>
       </c>
       <c r="N58">
-        <v>-2.498289120000001</v>
+        <v>-2.557687140000001</v>
       </c>
       <c r="O58">
-        <v>-0.6745380624000002</v>
+        <v>-0.6905755278000002</v>
       </c>
       <c r="P58">
-        <v>-1.8237510576</v>
+        <v>-1.8671116122</v>
       </c>
       <c r="Q58">
-        <v>-1.7477510576</v>
+        <v>-1.7911116122</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.169054585158459</v>
+        <v>0.1719209708598185</v>
       </c>
       <c r="T58">
-        <v>2.257451012399585</v>
+        <v>2.309949873153063</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>0.06721003254221027</v>
+        <v>0.06603090916427677</v>
       </c>
       <c r="W58">
-        <v>0.2199518743265468</v>
+        <v>0.2202299116190636</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.2489260464526306</v>
+        <v>0.2445589228306546</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1994570670925882</v>
+        <v>0.2013570670925882</v>
       </c>
       <c r="C59">
-        <v>-4.208403202482083</v>
+        <v>-4.56241237831162</v>
       </c>
       <c r="D59">
-        <v>8.359896797517917</v>
+        <v>8.257787621688383</v>
       </c>
       <c r="E59">
-        <v>11.4683</v>
+        <v>11.7202</v>
       </c>
       <c r="F59">
-        <v>14.3583</v>
+        <v>14.6102</v>
       </c>
       <c r="G59">
         <v>1.79</v>
@@ -6125,37 +6125,37 @@
         <v>0.828</v>
       </c>
       <c r="M59">
-        <v>3.38568714</v>
+        <v>3.445085160000001</v>
       </c>
       <c r="N59">
-        <v>-2.557687140000001</v>
+        <v>-2.617085160000001</v>
       </c>
       <c r="O59">
-        <v>-0.6905755278000002</v>
+        <v>-0.7066129932000003</v>
       </c>
       <c r="P59">
-        <v>-1.8671116122</v>
+        <v>-1.9104721668</v>
       </c>
       <c r="Q59">
-        <v>-1.7911116122</v>
+        <v>-1.8344721668</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1719209708598185</v>
+        <v>0.1749238511183856</v>
       </c>
       <c r="T59">
-        <v>2.309949873153063</v>
+        <v>2.364948679656708</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>0.06603090916427677</v>
+        <v>0.06489244521316855</v>
       </c>
       <c r="W59">
-        <v>0.2202299116190636</v>
+        <v>0.2204983614187349</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.2445589228306546</v>
+        <v>0.2403423896784019</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.2013570670925882</v>
+        <v>0.2032570670925882</v>
       </c>
       <c r="C60">
-        <v>-4.562412378311617</v>
+        <v>-4.913957295944828</v>
       </c>
       <c r="D60">
-        <v>8.257787621688381</v>
+        <v>8.158142704055171</v>
       </c>
       <c r="E60">
-        <v>11.7202</v>
+        <v>11.9721</v>
       </c>
       <c r="F60">
-        <v>14.6102</v>
+        <v>14.8621</v>
       </c>
       <c r="G60">
         <v>1.79</v>
@@ -6207,37 +6207,37 @@
         <v>0.828</v>
       </c>
       <c r="M60">
-        <v>3.44508516</v>
+        <v>3.50448318</v>
       </c>
       <c r="N60">
-        <v>-2.61708516</v>
+        <v>-2.67648318</v>
       </c>
       <c r="O60">
-        <v>-0.7066129932000002</v>
+        <v>-0.7226504586000002</v>
       </c>
       <c r="P60">
-        <v>-1.9104721668</v>
+        <v>-1.9538327214</v>
       </c>
       <c r="Q60">
-        <v>-1.8344721668</v>
+        <v>-1.8778327214</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1749238511183856</v>
+        <v>0.1780732133407852</v>
       </c>
       <c r="T60">
-        <v>2.364948679656707</v>
+        <v>2.422630354770286</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.06489244521316855</v>
+        <v>0.06379257326040298</v>
       </c>
       <c r="W60">
-        <v>0.2204983614187349</v>
+        <v>0.220757711225197</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.2403423896784019</v>
+        <v>0.2362687898533443</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.2032570670925882</v>
+        <v>0.2051570670925882</v>
       </c>
       <c r="C61">
-        <v>-4.913957295944828</v>
+        <v>-5.263126098769234</v>
       </c>
       <c r="D61">
-        <v>8.158142704055171</v>
+        <v>8.060873901230766</v>
       </c>
       <c r="E61">
-        <v>11.9721</v>
+        <v>12.224</v>
       </c>
       <c r="F61">
-        <v>14.8621</v>
+        <v>15.114</v>
       </c>
       <c r="G61">
         <v>1.79</v>
@@ -6289,37 +6289,37 @@
         <v>0.828</v>
       </c>
       <c r="M61">
-        <v>3.50448318</v>
+        <v>3.5638812</v>
       </c>
       <c r="N61">
-        <v>-2.67648318</v>
+        <v>-2.735881200000001</v>
       </c>
       <c r="O61">
-        <v>-0.7226504586000002</v>
+        <v>-0.7386879240000002</v>
       </c>
       <c r="P61">
-        <v>-1.9538327214</v>
+        <v>-1.997193276</v>
       </c>
       <c r="Q61">
-        <v>-1.8778327214</v>
+        <v>-1.921193276</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1780732133407852</v>
+        <v>0.1813800436743049</v>
       </c>
       <c r="T61">
-        <v>2.422630354770286</v>
+        <v>2.483196113639543</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.06379257326040298</v>
+        <v>0.06272936370606293</v>
       </c>
       <c r="W61">
-        <v>0.220757711225197</v>
+        <v>0.2210084160381104</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.2362687898533443</v>
+        <v>0.2323309766891218</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.2051570670925882</v>
+        <v>0.2070570670925882</v>
       </c>
       <c r="C62">
-        <v>-5.263126098769234</v>
+        <v>-5.610002775999416</v>
       </c>
       <c r="D62">
-        <v>8.060873901230766</v>
+        <v>7.965897224000583</v>
       </c>
       <c r="E62">
-        <v>12.224</v>
+        <v>12.4759</v>
       </c>
       <c r="F62">
-        <v>15.114</v>
+        <v>15.3659</v>
       </c>
       <c r="G62">
         <v>1.79</v>
@@ -6371,37 +6371,37 @@
         <v>0.828</v>
       </c>
       <c r="M62">
-        <v>3.5638812</v>
+        <v>3.62327922</v>
       </c>
       <c r="N62">
-        <v>-2.735881200000001</v>
+        <v>-2.79527922</v>
       </c>
       <c r="O62">
-        <v>-0.7386879240000002</v>
+        <v>-0.7547253894000001</v>
       </c>
       <c r="P62">
-        <v>-1.997193276</v>
+        <v>-2.0405538306</v>
       </c>
       <c r="Q62">
-        <v>-1.921193276</v>
+        <v>-1.9645538306</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1813800436743049</v>
+        <v>0.1848564550505691</v>
       </c>
       <c r="T62">
-        <v>2.483196113639543</v>
+        <v>2.546867808861069</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.06272936370606293</v>
+        <v>0.06170101348137337</v>
       </c>
       <c r="W62">
-        <v>0.2210084160381104</v>
+        <v>0.2212509010210922</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.2323309766891218</v>
+        <v>0.2285222721532346</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.2070570670925882</v>
+        <v>0.2089570670925882</v>
       </c>
       <c r="C63">
-        <v>-5.610002775999416</v>
+        <v>-5.954667404558302</v>
       </c>
       <c r="D63">
-        <v>7.965897224000583</v>
+        <v>7.873132595441698</v>
       </c>
       <c r="E63">
-        <v>12.4759</v>
+        <v>12.7278</v>
       </c>
       <c r="F63">
-        <v>15.3659</v>
+        <v>15.6178</v>
       </c>
       <c r="G63">
         <v>1.79</v>
@@ -6453,37 +6453,37 @@
         <v>0.828</v>
       </c>
       <c r="M63">
-        <v>3.62327922</v>
+        <v>3.68267724</v>
       </c>
       <c r="N63">
-        <v>-2.79527922</v>
+        <v>-2.85467724</v>
       </c>
       <c r="O63">
-        <v>-0.7547253894000001</v>
+        <v>-0.7707628548000002</v>
       </c>
       <c r="P63">
-        <v>-2.0405538306</v>
+        <v>-2.0839143852</v>
       </c>
       <c r="Q63">
-        <v>-1.9645538306</v>
+        <v>-2.0079143852</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1848564550505691</v>
+        <v>0.1885158354466367</v>
       </c>
       <c r="T63">
-        <v>2.546867808861069</v>
+        <v>2.613890645936361</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.06170101348137337</v>
+        <v>0.06070583584457702</v>
       </c>
       <c r="W63">
-        <v>0.2212509010210922</v>
+        <v>0.2214855639078488</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.2285222721532346</v>
+        <v>0.2248364290539889</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.2089570670925882</v>
+        <v>0.2108570670925881</v>
       </c>
       <c r="C64">
-        <v>-5.954667404558302</v>
+        <v>-6.297196374252451</v>
       </c>
       <c r="D64">
-        <v>7.873132595441698</v>
+        <v>7.78250362574755</v>
       </c>
       <c r="E64">
-        <v>12.7278</v>
+        <v>12.9797</v>
       </c>
       <c r="F64">
-        <v>15.6178</v>
+        <v>15.8697</v>
       </c>
       <c r="G64">
         <v>1.79</v>
@@ -6535,37 +6535,37 @@
         <v>0.828</v>
       </c>
       <c r="M64">
-        <v>3.68267724</v>
+        <v>3.74207526</v>
       </c>
       <c r="N64">
-        <v>-2.85467724</v>
+        <v>-2.914075260000001</v>
       </c>
       <c r="O64">
-        <v>-0.7707628548000002</v>
+        <v>-0.7868003202000002</v>
       </c>
       <c r="P64">
-        <v>-2.0839143852</v>
+        <v>-2.1272749398</v>
       </c>
       <c r="Q64">
-        <v>-2.0079143852</v>
+        <v>-2.0512749398</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1885158354466367</v>
+        <v>0.1923730201884377</v>
       </c>
       <c r="T64">
-        <v>2.613890645936361</v>
+        <v>2.684536339069776</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.06070583584457702</v>
+        <v>0.05974225114863136</v>
       </c>
       <c r="W64">
-        <v>0.2214855639078488</v>
+        <v>0.2217127771791527</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.2248364290539889</v>
+        <v>0.2212675968467828</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.2108570670925881</v>
+        <v>0.2127570670925882</v>
       </c>
       <c r="C65">
-        <v>-6.297196374252451</v>
+        <v>-6.637662597572129</v>
       </c>
       <c r="D65">
-        <v>7.78250362574755</v>
+        <v>7.693937402427871</v>
       </c>
       <c r="E65">
-        <v>12.9797</v>
+        <v>13.2316</v>
       </c>
       <c r="F65">
-        <v>15.8697</v>
+        <v>16.1216</v>
       </c>
       <c r="G65">
         <v>1.79</v>
@@ -6617,37 +6617,37 @@
         <v>0.828</v>
       </c>
       <c r="M65">
-        <v>3.74207526</v>
+        <v>3.80147328</v>
       </c>
       <c r="N65">
-        <v>-2.914075260000001</v>
+        <v>-2.97347328</v>
       </c>
       <c r="O65">
-        <v>-0.7868003202000002</v>
+        <v>-0.8028377856000002</v>
       </c>
       <c r="P65">
-        <v>-2.1272749398</v>
+        <v>-2.1706354944</v>
       </c>
       <c r="Q65">
-        <v>-2.0512749398</v>
+        <v>-2.0946354944</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1923730201884377</v>
+        <v>0.1964444929714499</v>
       </c>
       <c r="T65">
-        <v>2.684536339069776</v>
+        <v>2.759106792932826</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.05974225114863136</v>
+        <v>0.05880877847443399</v>
       </c>
       <c r="W65">
-        <v>0.2217127771791527</v>
+        <v>0.2219328900357285</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.2212675968467828</v>
+        <v>0.2178102906460518</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.2127570670925882</v>
+        <v>0.2146570670925882</v>
       </c>
       <c r="C66">
-        <v>-6.637662597572129</v>
+        <v>-6.976135705327206</v>
       </c>
       <c r="D66">
-        <v>7.693937402427871</v>
+        <v>7.607364294672793</v>
       </c>
       <c r="E66">
-        <v>13.2316</v>
+        <v>13.4835</v>
       </c>
       <c r="F66">
-        <v>16.1216</v>
+        <v>16.3735</v>
       </c>
       <c r="G66">
         <v>1.79</v>
@@ -6699,37 +6699,37 @@
         <v>0.828</v>
       </c>
       <c r="M66">
-        <v>3.80147328</v>
+        <v>3.8608713</v>
       </c>
       <c r="N66">
-        <v>-2.97347328</v>
+        <v>-3.0328713</v>
       </c>
       <c r="O66">
-        <v>-0.8028377856000002</v>
+        <v>-0.8188752510000001</v>
       </c>
       <c r="P66">
-        <v>-2.1706354944</v>
+        <v>-2.213996049</v>
       </c>
       <c r="Q66">
-        <v>-2.0946354944</v>
+        <v>-2.137996049</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1964444929714499</v>
+        <v>0.2007486213420627</v>
       </c>
       <c r="T66">
-        <v>2.759106792932826</v>
+        <v>2.83793841558805</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.05880877847443399</v>
+        <v>0.05790402803636577</v>
       </c>
       <c r="W66">
-        <v>0.2219328900357285</v>
+        <v>0.222146230189025</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.2178102906460518</v>
+        <v>0.214459363097651</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.2146570670925882</v>
+        <v>0.2165570670925882</v>
       </c>
       <c r="C67">
-        <v>-6.976135705327206</v>
+        <v>-7.312682229222123</v>
       </c>
       <c r="D67">
-        <v>7.607364294672793</v>
+        <v>7.522717770777881</v>
       </c>
       <c r="E67">
-        <v>13.4835</v>
+        <v>13.7354</v>
       </c>
       <c r="F67">
-        <v>16.3735</v>
+        <v>16.6254</v>
       </c>
       <c r="G67">
         <v>1.79</v>
@@ -6781,37 +6781,37 @@
         <v>0.828</v>
       </c>
       <c r="M67">
-        <v>3.8608713</v>
+        <v>3.920269320000001</v>
       </c>
       <c r="N67">
-        <v>-3.0328713</v>
+        <v>-3.092269320000001</v>
       </c>
       <c r="O67">
-        <v>-0.8188752510000001</v>
+        <v>-0.8349127164000003</v>
       </c>
       <c r="P67">
-        <v>-2.213996049</v>
+        <v>-2.257356603600001</v>
       </c>
       <c r="Q67">
-        <v>-2.137996049</v>
+        <v>-2.181356603600001</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.2007486213420627</v>
+        <v>0.2053059337344763</v>
       </c>
       <c r="T67">
-        <v>2.83793841558805</v>
+        <v>2.92140719251711</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.05790402803636577</v>
+        <v>0.05702669427823901</v>
       </c>
       <c r="W67">
-        <v>0.222146230189025</v>
+        <v>0.2223531054891912</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.214459363097651</v>
+        <v>0.2112099788082926</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.2165570670925882</v>
+        <v>0.2184570670925882</v>
       </c>
       <c r="C68">
-        <v>-7.312682229222123</v>
+        <v>-7.647365772375979</v>
       </c>
       <c r="D68">
-        <v>7.522717770777881</v>
+        <v>7.439934227624023</v>
       </c>
       <c r="E68">
-        <v>13.7354</v>
+        <v>13.9873</v>
       </c>
       <c r="F68">
-        <v>16.6254</v>
+        <v>16.8773</v>
       </c>
       <c r="G68">
         <v>1.79</v>
@@ -6863,37 +6863,37 @@
         <v>0.828</v>
       </c>
       <c r="M68">
-        <v>3.920269320000001</v>
+        <v>3.979667340000001</v>
       </c>
       <c r="N68">
-        <v>-3.092269320000001</v>
+        <v>-3.151667340000001</v>
       </c>
       <c r="O68">
-        <v>-0.8349127164000003</v>
+        <v>-0.8509501818000003</v>
       </c>
       <c r="P68">
-        <v>-2.257356603600001</v>
+        <v>-2.3007171582</v>
       </c>
       <c r="Q68">
-        <v>-2.181356603600001</v>
+        <v>-2.2247171582</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2053059337344763</v>
+        <v>0.2101394468779453</v>
       </c>
       <c r="T68">
-        <v>2.92140719251711</v>
+        <v>3.009934683199446</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.05702669427823901</v>
+        <v>0.05617554958751904</v>
       </c>
       <c r="W68">
-        <v>0.2223531054891912</v>
+        <v>0.222553805407263</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.2112099788082926</v>
+        <v>0.2080575910648853</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.2184570670925882</v>
+        <v>0.2203570670925882</v>
       </c>
       <c r="C69">
-        <v>-7.647365772375979</v>
+        <v>-7.980247168706313</v>
       </c>
       <c r="D69">
-        <v>7.439934227624023</v>
+        <v>7.358952831293687</v>
       </c>
       <c r="E69">
-        <v>13.9873</v>
+        <v>14.2392</v>
       </c>
       <c r="F69">
-        <v>16.8773</v>
+        <v>17.1292</v>
       </c>
       <c r="G69">
         <v>1.79</v>
@@ -6945,37 +6945,37 @@
         <v>0.828</v>
       </c>
       <c r="M69">
-        <v>3.979667340000001</v>
+        <v>4.03906536</v>
       </c>
       <c r="N69">
-        <v>-3.151667340000001</v>
+        <v>-3.211065360000001</v>
       </c>
       <c r="O69">
-        <v>-0.8509501818000003</v>
+        <v>-0.8669876472000002</v>
       </c>
       <c r="P69">
-        <v>-2.3007171582</v>
+        <v>-2.3440777128</v>
       </c>
       <c r="Q69">
-        <v>-2.2247171582</v>
+        <v>-2.2680777128</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2101394468779453</v>
+        <v>0.2152750545928811</v>
       </c>
       <c r="T69">
-        <v>3.009934683199446</v>
+        <v>3.103995142049429</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.05617554958751904</v>
+        <v>0.05534943856417317</v>
       </c>
       <c r="W69">
-        <v>0.222553805407263</v>
+        <v>0.222748602386568</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.2080575910648853</v>
+        <v>0.2049979206080488</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2203570670925882</v>
+        <v>0.2222570670925882</v>
       </c>
       <c r="C70">
-        <v>-7.980247168706313</v>
+        <v>-8.311384632015855</v>
       </c>
       <c r="D70">
-        <v>7.358952831293687</v>
+        <v>7.279715367984148</v>
       </c>
       <c r="E70">
-        <v>14.2392</v>
+        <v>14.4911</v>
       </c>
       <c r="F70">
-        <v>17.1292</v>
+        <v>17.3811</v>
       </c>
       <c r="G70">
         <v>1.79</v>
@@ -7027,37 +7027,37 @@
         <v>0.828</v>
       </c>
       <c r="M70">
-        <v>4.03906536</v>
+        <v>4.098463380000001</v>
       </c>
       <c r="N70">
-        <v>-3.211065360000001</v>
+        <v>-3.270463380000001</v>
       </c>
       <c r="O70">
-        <v>-0.8669876472000002</v>
+        <v>-0.8830251126000004</v>
       </c>
       <c r="P70">
-        <v>-2.3440777128</v>
+        <v>-2.387438267400001</v>
       </c>
       <c r="Q70">
-        <v>-2.2680777128</v>
+        <v>-2.311438267400001</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2152750545928811</v>
+        <v>0.2207419918378128</v>
       </c>
       <c r="T70">
-        <v>3.103995142049429</v>
+        <v>3.204124017599411</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.05534943856417317</v>
+        <v>0.0545472727878808</v>
       </c>
       <c r="W70">
-        <v>0.222748602386568</v>
+        <v>0.2229377530766177</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.2049979206080488</v>
+        <v>0.2020269362514103</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2222570670925882</v>
+        <v>0.2241570670925882</v>
       </c>
       <c r="C71">
-        <v>-8.311384632015855</v>
+        <v>-8.640833895550168</v>
       </c>
       <c r="D71">
-        <v>7.279715367984148</v>
+        <v>7.202166104449835</v>
       </c>
       <c r="E71">
-        <v>14.4911</v>
+        <v>14.743</v>
       </c>
       <c r="F71">
-        <v>17.3811</v>
+        <v>17.633</v>
       </c>
       <c r="G71">
         <v>1.79</v>
@@ -7109,37 +7109,37 @@
         <v>0.828</v>
       </c>
       <c r="M71">
-        <v>4.098463380000001</v>
+        <v>4.157861400000001</v>
       </c>
       <c r="N71">
-        <v>-3.270463380000001</v>
+        <v>-3.329861400000001</v>
       </c>
       <c r="O71">
-        <v>-0.8830251126000004</v>
+        <v>-0.8990625780000003</v>
       </c>
       <c r="P71">
-        <v>-2.387438267400001</v>
+        <v>-2.430798822000001</v>
       </c>
       <c r="Q71">
-        <v>-2.311438267400001</v>
+        <v>-2.354798822000001</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2207419918378128</v>
+        <v>0.2265733915657399</v>
       </c>
       <c r="T71">
-        <v>3.204124017599411</v>
+        <v>3.310928151519391</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.0545472727878808</v>
+        <v>0.05376802603376821</v>
       </c>
       <c r="W71">
-        <v>0.2229377530766177</v>
+        <v>0.2231214994612375</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.2020269362514103</v>
+        <v>0.1991408371621045</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2241570670925882</v>
+        <v>0.2260570670925882</v>
       </c>
       <c r="C72">
-        <v>-8.640833895550168</v>
+        <v>-8.968648342729235</v>
       </c>
       <c r="D72">
-        <v>7.202166104449835</v>
+        <v>7.126251657270766</v>
       </c>
       <c r="E72">
-        <v>14.743</v>
+        <v>14.9949</v>
       </c>
       <c r="F72">
-        <v>17.633</v>
+        <v>17.8849</v>
       </c>
       <c r="G72">
         <v>1.79</v>
@@ -7191,37 +7191,37 @@
         <v>0.828</v>
       </c>
       <c r="M72">
-        <v>4.157861400000001</v>
+        <v>4.21725942</v>
       </c>
       <c r="N72">
-        <v>-3.329861400000001</v>
+        <v>-3.389259420000001</v>
       </c>
       <c r="O72">
-        <v>-0.8990625780000003</v>
+        <v>-0.9151000434000002</v>
       </c>
       <c r="P72">
-        <v>-2.430798822000001</v>
+        <v>-2.4741593766</v>
       </c>
       <c r="Q72">
-        <v>-2.354798822000001</v>
+        <v>-2.3981593766</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2265733915657399</v>
+        <v>0.2328069567921447</v>
       </c>
       <c r="T72">
-        <v>3.310928151519391</v>
+        <v>3.425098087778681</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.05376802603376821</v>
+        <v>0.05301072989244755</v>
       </c>
       <c r="W72">
-        <v>0.2231214994612375</v>
+        <v>0.2233000698913609</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.1991408371621045</v>
+        <v>0.1963360366386946</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2260570670925882</v>
+        <v>0.2279570670925882</v>
       </c>
       <c r="C73">
-        <v>-8.968648342729232</v>
+        <v>-9.294879129697453</v>
       </c>
       <c r="D73">
-        <v>7.126251657270766</v>
+        <v>7.051920870302547</v>
       </c>
       <c r="E73">
-        <v>14.9949</v>
+        <v>15.2468</v>
       </c>
       <c r="F73">
-        <v>17.8849</v>
+        <v>18.1368</v>
       </c>
       <c r="G73">
         <v>1.79</v>
@@ -7273,37 +7273,37 @@
         <v>0.828</v>
       </c>
       <c r="M73">
-        <v>4.21725942</v>
+        <v>4.27665744</v>
       </c>
       <c r="N73">
-        <v>-3.38925942</v>
+        <v>-3.44865744</v>
       </c>
       <c r="O73">
-        <v>-0.9151000434</v>
+        <v>-0.9311375088000001</v>
       </c>
       <c r="P73">
-        <v>-2.4741593766</v>
+        <v>-2.5175199312</v>
       </c>
       <c r="Q73">
-        <v>-2.3981593766</v>
+        <v>-2.4415199312</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2328069567921446</v>
+        <v>0.2394857766775784</v>
       </c>
       <c r="T73">
-        <v>3.42509808777868</v>
+        <v>3.547423019485061</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.05301072989244755</v>
+        <v>0.05227446975505244</v>
       </c>
       <c r="W73">
-        <v>0.2233000698913609</v>
+        <v>0.2234736800317586</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.1963360366386946</v>
+        <v>0.1936091472409349</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2279570670925882</v>
+        <v>0.2298570670925882</v>
       </c>
       <c r="C74">
-        <v>-9.294879129697453</v>
+        <v>-9.619575300283149</v>
       </c>
       <c r="D74">
-        <v>7.051920870302547</v>
+        <v>6.97912469971685</v>
       </c>
       <c r="E74">
-        <v>15.2468</v>
+        <v>15.4987</v>
       </c>
       <c r="F74">
-        <v>18.1368</v>
+        <v>18.3887</v>
       </c>
       <c r="G74">
         <v>1.79</v>
@@ -7355,37 +7355,37 @@
         <v>0.828</v>
       </c>
       <c r="M74">
-        <v>4.27665744</v>
+        <v>4.33605546</v>
       </c>
       <c r="N74">
-        <v>-3.44865744</v>
+        <v>-3.50805546</v>
       </c>
       <c r="O74">
-        <v>-0.9311375088000001</v>
+        <v>-0.9471749742000001</v>
       </c>
       <c r="P74">
-        <v>-2.5175199312</v>
+        <v>-2.5608804858</v>
       </c>
       <c r="Q74">
-        <v>-2.4415199312</v>
+        <v>-2.4848804858</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2394857766775784</v>
+        <v>0.2466593239619331</v>
       </c>
       <c r="T74">
-        <v>3.547423019485061</v>
+        <v>3.678809057243767</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.05227446975505244</v>
+        <v>0.0515583811282709</v>
       </c>
       <c r="W74">
-        <v>0.2234736800317586</v>
+        <v>0.2236425337299537</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.1936091472409349</v>
+        <v>0.190956967141744</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2298570670925882</v>
+        <v>0.2317570670925881</v>
       </c>
       <c r="C75">
-        <v>-9.619575300283149</v>
+        <v>-9.942783893910619</v>
       </c>
       <c r="D75">
-        <v>6.97912469971685</v>
+        <v>6.90781610608938</v>
       </c>
       <c r="E75">
-        <v>15.4987</v>
+        <v>15.7506</v>
       </c>
       <c r="F75">
-        <v>18.3887</v>
+        <v>18.6406</v>
       </c>
       <c r="G75">
         <v>1.79</v>
@@ -7437,37 +7437,37 @@
         <v>0.828</v>
       </c>
       <c r="M75">
-        <v>4.33605546</v>
+        <v>4.39545348</v>
       </c>
       <c r="N75">
-        <v>-3.50805546</v>
+        <v>-3.56745348</v>
       </c>
       <c r="O75">
-        <v>-0.9471749742000001</v>
+        <v>-0.9632124396</v>
       </c>
       <c r="P75">
-        <v>-2.5608804858</v>
+        <v>-2.6042410404</v>
       </c>
       <c r="Q75">
-        <v>-2.4848804858</v>
+        <v>-2.5282410404</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2466593239619331</v>
+        <v>0.2543846825758536</v>
       </c>
       <c r="T75">
-        <v>3.678809057243767</v>
+        <v>3.820301713291604</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.0515583811282709</v>
+        <v>0.05086164624815914</v>
       </c>
       <c r="W75">
-        <v>0.2236425337299537</v>
+        <v>0.2238068238146841</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.190956967141744</v>
+        <v>0.1883764675857745</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2317570670925881</v>
+        <v>0.2336570670925882</v>
       </c>
       <c r="C76">
-        <v>-9.942783893910619</v>
+        <v>-10.26455004696358</v>
       </c>
       <c r="D76">
-        <v>6.90781610608938</v>
+        <v>6.837949953036424</v>
       </c>
       <c r="E76">
-        <v>15.7506</v>
+        <v>16.0025</v>
       </c>
       <c r="F76">
-        <v>18.6406</v>
+        <v>18.8925</v>
       </c>
       <c r="G76">
         <v>1.79</v>
@@ -7519,37 +7519,37 @@
         <v>0.828</v>
       </c>
       <c r="M76">
-        <v>4.39545348</v>
+        <v>4.4548515</v>
       </c>
       <c r="N76">
-        <v>-3.56745348</v>
+        <v>-3.6268515</v>
       </c>
       <c r="O76">
-        <v>-0.9632124396</v>
+        <v>-0.9792499050000002</v>
       </c>
       <c r="P76">
-        <v>-2.6042410404</v>
+        <v>-2.647601595</v>
       </c>
       <c r="Q76">
-        <v>-2.5282410404</v>
+        <v>-2.571601595</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2543846825758536</v>
+        <v>0.2627280698788877</v>
       </c>
       <c r="T76">
-        <v>3.820301713291604</v>
+        <v>3.973113781823268</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.05086164624815914</v>
+        <v>0.05018349096485034</v>
       </c>
       <c r="W76">
-        <v>0.2238068238146841</v>
+        <v>0.2239667328304883</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.1883764675857745</v>
+        <v>0.1858647813512976</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2336570670925882</v>
+        <v>0.2355570670925882</v>
       </c>
       <c r="C77">
-        <v>-10.26455004696358</v>
+        <v>-10.58491708805897</v>
       </c>
       <c r="D77">
-        <v>6.837949953036424</v>
+        <v>6.769482911941034</v>
       </c>
       <c r="E77">
-        <v>16.0025</v>
+        <v>16.2544</v>
       </c>
       <c r="F77">
-        <v>18.8925</v>
+        <v>19.1444</v>
       </c>
       <c r="G77">
         <v>1.79</v>
@@ -7601,37 +7601,37 @@
         <v>0.828</v>
       </c>
       <c r="M77">
-        <v>4.4548515</v>
+        <v>4.514249520000001</v>
       </c>
       <c r="N77">
-        <v>-3.6268515</v>
+        <v>-3.686249520000001</v>
       </c>
       <c r="O77">
-        <v>-0.9792499050000002</v>
+        <v>-0.9952873704000004</v>
       </c>
       <c r="P77">
-        <v>-2.647601595</v>
+        <v>-2.690962149600001</v>
       </c>
       <c r="Q77">
-        <v>-2.571601595</v>
+        <v>-2.614962149600001</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2627280698788877</v>
+        <v>0.2717667394571748</v>
       </c>
       <c r="T77">
-        <v>3.973113781823268</v>
+        <v>4.138660189399239</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.05018349096485034</v>
+        <v>0.04952318187320757</v>
       </c>
       <c r="W77">
-        <v>0.2239667328304883</v>
+        <v>0.2241224337142977</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.1858647813512976</v>
+        <v>0.183419192122991</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2355570670925882</v>
+        <v>0.2374570670925882</v>
       </c>
       <c r="C78">
-        <v>-10.58491708805897</v>
+        <v>-10.90392662765384</v>
       </c>
       <c r="D78">
-        <v>6.769482911941034</v>
+        <v>6.702373372346157</v>
       </c>
       <c r="E78">
-        <v>16.2544</v>
+        <v>16.5063</v>
       </c>
       <c r="F78">
-        <v>19.1444</v>
+        <v>19.3963</v>
       </c>
       <c r="G78">
         <v>1.79</v>
@@ -7683,37 +7683,37 @@
         <v>0.828</v>
       </c>
       <c r="M78">
-        <v>4.514249520000001</v>
+        <v>4.573647540000001</v>
       </c>
       <c r="N78">
-        <v>-3.686249520000001</v>
+        <v>-3.745647540000001</v>
       </c>
       <c r="O78">
-        <v>-0.9952873704000004</v>
+        <v>-1.0113248358</v>
       </c>
       <c r="P78">
-        <v>-2.690962149600001</v>
+        <v>-2.7343227042</v>
       </c>
       <c r="Q78">
-        <v>-2.614962149600001</v>
+        <v>-2.6583227042</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2717667394571748</v>
+        <v>0.2815913803031389</v>
       </c>
       <c r="T78">
-        <v>4.138660189399239</v>
+        <v>4.318601936764423</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.04952318187320757</v>
+        <v>0.04888002366706202</v>
       </c>
       <c r="W78">
-        <v>0.2241224337142977</v>
+        <v>0.2242740904193068</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.183419192122991</v>
+        <v>0.1810371246928223</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2374570670925882</v>
+        <v>0.2393570670925882</v>
       </c>
       <c r="C79">
-        <v>-10.90392662765384</v>
+        <v>-11.22161864237458</v>
       </c>
       <c r="D79">
-        <v>6.702373372346157</v>
+        <v>6.636581357625422</v>
       </c>
       <c r="E79">
-        <v>16.5063</v>
+        <v>16.7582</v>
       </c>
       <c r="F79">
-        <v>19.3963</v>
+        <v>19.6482</v>
       </c>
       <c r="G79">
         <v>1.79</v>
@@ -7765,37 +7765,37 @@
         <v>0.828</v>
       </c>
       <c r="M79">
-        <v>4.573647540000001</v>
+        <v>4.633045560000001</v>
       </c>
       <c r="N79">
-        <v>-3.745647540000001</v>
+        <v>-3.805045560000001</v>
       </c>
       <c r="O79">
-        <v>-1.0113248358</v>
+        <v>-1.0273623012</v>
       </c>
       <c r="P79">
-        <v>-2.7343227042</v>
+        <v>-2.777683258800001</v>
       </c>
       <c r="Q79">
-        <v>-2.6583227042</v>
+        <v>-2.701683258800001</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2815913803031389</v>
+        <v>0.2923091703169179</v>
       </c>
       <c r="T79">
-        <v>4.318601936764423</v>
+        <v>4.514902024799169</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.04888002366706202</v>
+        <v>0.04825335669697147</v>
       </c>
       <c r="W79">
-        <v>0.2242740904193068</v>
+        <v>0.2244218584908541</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.1810371246928223</v>
+        <v>0.1787161359147091</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2393570670925882</v>
+        <v>0.2412570670925882</v>
       </c>
       <c r="C80">
-        <v>-11.22161864237458</v>
+        <v>-11.53803155442762</v>
       </c>
       <c r="D80">
-        <v>6.636581357625422</v>
+        <v>6.572068445572388</v>
       </c>
       <c r="E80">
-        <v>16.7582</v>
+        <v>17.0101</v>
       </c>
       <c r="F80">
-        <v>19.6482</v>
+        <v>19.9001</v>
       </c>
       <c r="G80">
         <v>1.79</v>
@@ -7847,37 +7847,37 @@
         <v>0.828</v>
       </c>
       <c r="M80">
-        <v>4.633045560000001</v>
+        <v>4.692443580000001</v>
       </c>
       <c r="N80">
-        <v>-3.805045560000001</v>
+        <v>-3.864443580000001</v>
       </c>
       <c r="O80">
-        <v>-1.0273623012</v>
+        <v>-1.0433997666</v>
       </c>
       <c r="P80">
-        <v>-2.777683258800001</v>
+        <v>-2.821043813400001</v>
       </c>
       <c r="Q80">
-        <v>-2.701683258800001</v>
+        <v>-2.745043813400001</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2923091703169179</v>
+        <v>0.3040477022367712</v>
       </c>
       <c r="T80">
-        <v>4.514902024799169</v>
+        <v>4.729897359313416</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.04825335669697147</v>
+        <v>0.04764255471346551</v>
       </c>
       <c r="W80">
-        <v>0.2244218584908541</v>
+        <v>0.2245658855985649</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.1787161359147091</v>
+        <v>0.1764539063461685</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2412570670925882</v>
+        <v>0.2431570670925882</v>
       </c>
       <c r="C81">
-        <v>-11.53803155442762</v>
+        <v>-11.85320230642318</v>
       </c>
       <c r="D81">
-        <v>6.572068445572388</v>
+        <v>6.50879769357682</v>
       </c>
       <c r="E81">
-        <v>17.0101</v>
+        <v>17.262</v>
       </c>
       <c r="F81">
-        <v>19.9001</v>
+        <v>20.152</v>
       </c>
       <c r="G81">
         <v>1.79</v>
@@ -7929,37 +7929,37 @@
         <v>0.828</v>
       </c>
       <c r="M81">
-        <v>4.692443580000001</v>
+        <v>4.751841600000001</v>
       </c>
       <c r="N81">
-        <v>-3.864443580000001</v>
+        <v>-3.923841600000001</v>
       </c>
       <c r="O81">
-        <v>-1.0433997666</v>
+        <v>-1.059437232</v>
       </c>
       <c r="P81">
-        <v>-2.821043813400001</v>
+        <v>-2.864404368000001</v>
       </c>
       <c r="Q81">
-        <v>-2.745043813400001</v>
+        <v>-2.788404368000001</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.3040477022367712</v>
+        <v>0.3169600873486098</v>
       </c>
       <c r="T81">
-        <v>4.729897359313416</v>
+        <v>4.966392227279087</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.04764255471346551</v>
+        <v>0.04704702277954719</v>
       </c>
       <c r="W81">
-        <v>0.2245658855985649</v>
+        <v>0.2247063120285828</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.1764539063461685</v>
+        <v>0.1742482325168414</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2431570670925882</v>
+        <v>0.2450570670925882</v>
       </c>
       <c r="C82">
-        <v>-11.85320230642318</v>
+        <v>-12.16716643191816</v>
       </c>
       <c r="D82">
-        <v>6.50879769357682</v>
+        <v>6.446733568081842</v>
       </c>
       <c r="E82">
-        <v>17.262</v>
+        <v>17.5139</v>
       </c>
       <c r="F82">
-        <v>20.152</v>
+        <v>20.4039</v>
       </c>
       <c r="G82">
         <v>1.79</v>
@@ -8011,37 +8011,37 @@
         <v>0.828</v>
       </c>
       <c r="M82">
-        <v>4.751841600000001</v>
+        <v>4.811239620000001</v>
       </c>
       <c r="N82">
-        <v>-3.923841600000001</v>
+        <v>-3.983239620000001</v>
       </c>
       <c r="O82">
-        <v>-1.059437232</v>
+        <v>-1.0754746974</v>
       </c>
       <c r="P82">
-        <v>-2.864404368000001</v>
+        <v>-2.907764922600001</v>
       </c>
       <c r="Q82">
-        <v>-2.788404368000001</v>
+        <v>-2.831764922600001</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.3169600873486098</v>
+        <v>0.3312316708932735</v>
       </c>
       <c r="T82">
-        <v>4.966392227279087</v>
+        <v>5.227781291872724</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.04704702277954719</v>
+        <v>0.04646619533782438</v>
       </c>
       <c r="W82">
-        <v>0.2247063120285828</v>
+        <v>0.224843271139341</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.1742482325168414</v>
+        <v>0.1720970197697199</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2450570670925882</v>
+        <v>0.2469570670925882</v>
       </c>
       <c r="C83">
-        <v>-12.16716643191816</v>
+        <v>-12.47995812196113</v>
       </c>
       <c r="D83">
-        <v>6.446733568081842</v>
+        <v>6.385841878038868</v>
       </c>
       <c r="E83">
-        <v>17.5139</v>
+        <v>17.7658</v>
       </c>
       <c r="F83">
-        <v>20.4039</v>
+        <v>20.6558</v>
       </c>
       <c r="G83">
         <v>1.79</v>
@@ -8093,37 +8093,37 @@
         <v>0.828</v>
       </c>
       <c r="M83">
-        <v>4.811239620000001</v>
+        <v>4.870637640000001</v>
       </c>
       <c r="N83">
-        <v>-3.983239620000001</v>
+        <v>-4.042637640000001</v>
       </c>
       <c r="O83">
-        <v>-1.0754746974</v>
+        <v>-1.0915121628</v>
       </c>
       <c r="P83">
-        <v>-2.907764922600001</v>
+        <v>-2.951125477200001</v>
       </c>
       <c r="Q83">
-        <v>-2.831764922600001</v>
+        <v>-2.875125477200001</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3312316708932735</v>
+        <v>0.3470889859428998</v>
       </c>
       <c r="T83">
-        <v>5.227781291872724</v>
+        <v>5.518213585865652</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.04646619533782438</v>
+        <v>0.04589953441907043</v>
       </c>
       <c r="W83">
-        <v>0.224843271139341</v>
+        <v>0.2249768897839832</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.1720970197697199</v>
+        <v>0.1699982756261869</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2469570670925882</v>
+        <v>0.2488570670925881</v>
       </c>
       <c r="C84">
-        <v>-12.47995812196113</v>
+        <v>-12.79161028790147</v>
       </c>
       <c r="D84">
-        <v>6.385841878038868</v>
+        <v>6.326089712098535</v>
       </c>
       <c r="E84">
-        <v>17.7658</v>
+        <v>18.0177</v>
       </c>
       <c r="F84">
-        <v>20.6558</v>
+        <v>20.9077</v>
       </c>
       <c r="G84">
         <v>1.79</v>
@@ -8175,37 +8175,37 @@
         <v>0.828</v>
       </c>
       <c r="M84">
-        <v>4.870637640000001</v>
+        <v>4.930035660000001</v>
       </c>
       <c r="N84">
-        <v>-4.042637640000001</v>
+        <v>-4.10203566</v>
       </c>
       <c r="O84">
-        <v>-1.0915121628</v>
+        <v>-1.1075496282</v>
       </c>
       <c r="P84">
-        <v>-2.951125477200001</v>
+        <v>-2.9944860318</v>
       </c>
       <c r="Q84">
-        <v>-2.875125477200001</v>
+        <v>-2.9184860318</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3470889859428998</v>
+        <v>0.3648118674689527</v>
       </c>
       <c r="T84">
-        <v>5.518213585865652</v>
+        <v>5.84281438503422</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.04589953441907043</v>
+        <v>0.04534652798028645</v>
       </c>
       <c r="W84">
-        <v>0.2249768897839832</v>
+        <v>0.2251072887022484</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.1699982756261869</v>
+        <v>0.1679501036306906</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2488570670925881</v>
+        <v>0.2507570670925882</v>
       </c>
       <c r="C85">
-        <v>-12.79161028790147</v>
+        <v>-13.10215462070488</v>
       </c>
       <c r="D85">
-        <v>6.326089712098535</v>
+        <v>6.267445379295128</v>
       </c>
       <c r="E85">
-        <v>18.0177</v>
+        <v>18.2696</v>
       </c>
       <c r="F85">
-        <v>20.9077</v>
+        <v>21.1596</v>
       </c>
       <c r="G85">
         <v>1.79</v>
@@ -8257,37 +8257,37 @@
         <v>0.828</v>
       </c>
       <c r="M85">
-        <v>4.930035660000001</v>
+        <v>4.989433680000001</v>
       </c>
       <c r="N85">
-        <v>-4.10203566</v>
+        <v>-4.161433680000001</v>
       </c>
       <c r="O85">
-        <v>-1.1075496282</v>
+        <v>-1.1235870936</v>
       </c>
       <c r="P85">
-        <v>-2.9944860318</v>
+        <v>-3.037846586400001</v>
       </c>
       <c r="Q85">
-        <v>-2.9184860318</v>
+        <v>-2.961846586400001</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3648118674689527</v>
+        <v>0.3847501091857624</v>
       </c>
       <c r="T85">
-        <v>5.84281438503422</v>
+        <v>6.207990284098861</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.04534652798028645</v>
+        <v>0.04480668836147352</v>
       </c>
       <c r="W85">
-        <v>0.2251072887022484</v>
+        <v>0.2252345828843646</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.1679501036306906</v>
+        <v>0.1659506976350872</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2507570670925882</v>
+        <v>0.2526570670925882</v>
       </c>
       <c r="C86">
-        <v>-13.10215462070487</v>
+        <v>-13.41162164700004</v>
       </c>
       <c r="D86">
-        <v>6.267445379295131</v>
+        <v>6.209878352999961</v>
       </c>
       <c r="E86">
-        <v>18.2696</v>
+        <v>18.5215</v>
       </c>
       <c r="F86">
-        <v>21.1596</v>
+        <v>21.4115</v>
       </c>
       <c r="G86">
         <v>1.79</v>
@@ -8339,37 +8339,37 @@
         <v>0.828</v>
       </c>
       <c r="M86">
-        <v>4.98943368</v>
+        <v>5.0488317</v>
       </c>
       <c r="N86">
-        <v>-4.16143368</v>
+        <v>-4.2208317</v>
       </c>
       <c r="O86">
-        <v>-1.1235870936</v>
+        <v>-1.139624559</v>
       </c>
       <c r="P86">
-        <v>-3.0378465864</v>
+        <v>-3.081207141</v>
       </c>
       <c r="Q86">
-        <v>-2.9618465864</v>
+        <v>-3.005207141</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3847501091857621</v>
+        <v>0.4073467831314797</v>
       </c>
       <c r="T86">
-        <v>6.207990284098856</v>
+        <v>6.621856303038781</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.04480668836147352</v>
+        <v>0.04427955085133854</v>
       </c>
       <c r="W86">
-        <v>0.2252345828843646</v>
+        <v>0.2253588819092544</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.1659506976350872</v>
+        <v>0.1639983364864391</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2526570670925882</v>
+        <v>0.2545570670925882</v>
       </c>
       <c r="C87">
-        <v>-13.41162164700004</v>
+        <v>-13.72004078206466</v>
       </c>
       <c r="D87">
-        <v>6.209878352999961</v>
+        <v>6.153359217935341</v>
       </c>
       <c r="E87">
-        <v>18.5215</v>
+        <v>18.7734</v>
       </c>
       <c r="F87">
-        <v>21.4115</v>
+        <v>21.6634</v>
       </c>
       <c r="G87">
         <v>1.79</v>
@@ -8421,37 +8421,37 @@
         <v>0.828</v>
       </c>
       <c r="M87">
-        <v>5.0488317</v>
+        <v>5.10822972</v>
       </c>
       <c r="N87">
-        <v>-4.2208317</v>
+        <v>-4.280229719999999</v>
       </c>
       <c r="O87">
-        <v>-1.139624559</v>
+        <v>-1.1556620244</v>
       </c>
       <c r="P87">
-        <v>-3.081207141</v>
+        <v>-3.1245676956</v>
       </c>
       <c r="Q87">
-        <v>-3.005207141</v>
+        <v>-3.0485676956</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.4073467831314797</v>
+        <v>0.4331715533551568</v>
       </c>
       <c r="T87">
-        <v>6.621856303038781</v>
+        <v>7.094846038970123</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.04427955085133854</v>
+        <v>0.04376467235306716</v>
       </c>
       <c r="W87">
-        <v>0.2253588819092544</v>
+        <v>0.2254802902591468</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.1639983364864391</v>
+        <v>0.162091379085434</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2545570670925882</v>
+        <v>0.2564570670925881</v>
       </c>
       <c r="C88">
-        <v>-13.72004078206466</v>
+        <v>-14.02744037994399</v>
       </c>
       <c r="D88">
-        <v>6.153359217935341</v>
+        <v>6.097859620056014</v>
       </c>
       <c r="E88">
-        <v>18.7734</v>
+        <v>19.0253</v>
       </c>
       <c r="F88">
-        <v>21.6634</v>
+        <v>21.9153</v>
       </c>
       <c r="G88">
         <v>1.79</v>
@@ -8503,37 +8503,37 @@
         <v>0.828</v>
       </c>
       <c r="M88">
-        <v>5.10822972</v>
+        <v>5.16762774</v>
       </c>
       <c r="N88">
-        <v>-4.280229719999999</v>
+        <v>-4.33962774</v>
       </c>
       <c r="O88">
-        <v>-1.1556620244</v>
+        <v>-1.1716994898</v>
       </c>
       <c r="P88">
-        <v>-3.1245676956</v>
+        <v>-3.1679282502</v>
       </c>
       <c r="Q88">
-        <v>-3.0485676956</v>
+        <v>-3.0919282502</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.4331715533551568</v>
+        <v>0.4629693651517072</v>
       </c>
       <c r="T88">
-        <v>7.094846038970123</v>
+        <v>7.640603426583208</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.04376467235306716</v>
+        <v>0.04326163014211237</v>
       </c>
       <c r="W88">
-        <v>0.2254802902591468</v>
+        <v>0.2255989076124899</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.162091379085434</v>
+        <v>0.1602282597856014</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2564570670925881</v>
+        <v>0.2583570670925882</v>
       </c>
       <c r="C89">
-        <v>-14.02744037994399</v>
+        <v>-14.33384778088145</v>
       </c>
       <c r="D89">
-        <v>6.097859620056014</v>
+        <v>6.043352219118553</v>
       </c>
       <c r="E89">
-        <v>19.0253</v>
+        <v>19.2772</v>
       </c>
       <c r="F89">
-        <v>21.9153</v>
+        <v>22.1672</v>
       </c>
       <c r="G89">
         <v>1.79</v>
@@ -8585,37 +8585,37 @@
         <v>0.828</v>
       </c>
       <c r="M89">
-        <v>5.16762774</v>
+        <v>5.22702576</v>
       </c>
       <c r="N89">
-        <v>-4.33962774</v>
+        <v>-4.39902576</v>
       </c>
       <c r="O89">
-        <v>-1.1716994898</v>
+        <v>-1.1877369552</v>
       </c>
       <c r="P89">
-        <v>-3.1679282502</v>
+        <v>-3.2112888048</v>
       </c>
       <c r="Q89">
-        <v>-3.0919282502</v>
+        <v>-3.1352888048</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.4629693651517072</v>
+        <v>0.4977334789143497</v>
       </c>
       <c r="T89">
-        <v>7.640603426583208</v>
+        <v>8.277320378798478</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.04326163014211237</v>
+        <v>0.04277002070867927</v>
       </c>
       <c r="W89">
-        <v>0.2255989076124899</v>
+        <v>0.2257148291168934</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.1602282597856014</v>
+        <v>0.1584074841062195</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2583570670925882</v>
+        <v>0.2602570670925882</v>
       </c>
       <c r="C90">
-        <v>-14.33384778088145</v>
+        <v>-14.63928935622794</v>
       </c>
       <c r="D90">
-        <v>6.043352219118553</v>
+        <v>5.989810643772061</v>
       </c>
       <c r="E90">
-        <v>19.2772</v>
+        <v>19.5291</v>
       </c>
       <c r="F90">
-        <v>22.1672</v>
+        <v>22.4191</v>
       </c>
       <c r="G90">
         <v>1.79</v>
@@ -8667,37 +8667,37 @@
         <v>0.828</v>
       </c>
       <c r="M90">
-        <v>5.22702576</v>
+        <v>5.286423780000001</v>
       </c>
       <c r="N90">
-        <v>-4.39902576</v>
+        <v>-4.45842378</v>
       </c>
       <c r="O90">
-        <v>-1.1877369552</v>
+        <v>-1.2037744206</v>
       </c>
       <c r="P90">
-        <v>-3.2112888048</v>
+        <v>-3.2546493594</v>
       </c>
       <c r="Q90">
-        <v>-3.1352888048</v>
+        <v>-3.1786493594</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.4977334789143497</v>
+        <v>0.5388183406338359</v>
       </c>
       <c r="T90">
-        <v>8.277320378798478</v>
+        <v>9.02980404959834</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.04277002070867927</v>
+        <v>0.04228945867824466</v>
       </c>
       <c r="W90">
-        <v>0.2257148291168934</v>
+        <v>0.2258281456436699</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.1584074841062195</v>
+        <v>0.1566276247342395</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2602570670925882</v>
+        <v>0.2621570670925882</v>
       </c>
       <c r="C91">
-        <v>-14.63928935622794</v>
+        <v>-14.94379055098483</v>
       </c>
       <c r="D91">
-        <v>5.989810643772061</v>
+        <v>5.937209449015171</v>
       </c>
       <c r="E91">
-        <v>19.5291</v>
+        <v>19.781</v>
       </c>
       <c r="F91">
-        <v>22.4191</v>
+        <v>22.671</v>
       </c>
       <c r="G91">
         <v>1.79</v>
@@ -8749,37 +8749,37 @@
         <v>0.828</v>
       </c>
       <c r="M91">
-        <v>5.286423780000001</v>
+        <v>5.345821800000001</v>
       </c>
       <c r="N91">
-        <v>-4.45842378</v>
+        <v>-4.517821800000001</v>
       </c>
       <c r="O91">
-        <v>-1.2037744206</v>
+        <v>-1.219811886</v>
       </c>
       <c r="P91">
-        <v>-3.2546493594</v>
+        <v>-3.298009914000001</v>
       </c>
       <c r="Q91">
-        <v>-3.1786493594</v>
+        <v>-3.222009914</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.5388183406338359</v>
+        <v>0.5881201746972196</v>
       </c>
       <c r="T91">
-        <v>9.02980404959834</v>
+        <v>9.932784454558174</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.04228945867824466</v>
+        <v>0.04181957580404194</v>
       </c>
       <c r="W91">
-        <v>0.2258281456436699</v>
+        <v>0.2259389440254069</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.1566276247342395</v>
+        <v>0.154887317792748</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2621570670925882</v>
+        <v>0.2640570670925882</v>
       </c>
       <c r="C92">
-        <v>-14.94379055098483</v>
+        <v>-15.24737592412486</v>
       </c>
       <c r="D92">
-        <v>5.937209449015171</v>
+        <v>5.885524075875141</v>
       </c>
       <c r="E92">
-        <v>19.781</v>
+        <v>20.0329</v>
       </c>
       <c r="F92">
-        <v>22.671</v>
+        <v>22.9229</v>
       </c>
       <c r="G92">
         <v>1.79</v>
@@ -8831,37 +8831,37 @@
         <v>0.828</v>
       </c>
       <c r="M92">
-        <v>5.345821800000001</v>
+        <v>5.405219820000001</v>
       </c>
       <c r="N92">
-        <v>-4.517821800000001</v>
+        <v>-4.577219820000001</v>
       </c>
       <c r="O92">
-        <v>-1.219811886</v>
+        <v>-1.2358493514</v>
       </c>
       <c r="P92">
-        <v>-3.298009914000001</v>
+        <v>-3.341370468600001</v>
       </c>
       <c r="Q92">
-        <v>-3.222009914</v>
+        <v>-3.2653704686</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.5881201746972196</v>
+        <v>0.6483779718857996</v>
       </c>
       <c r="T92">
-        <v>9.932784454558174</v>
+        <v>11.03642717173131</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.04181957580404194</v>
+        <v>0.04136002002597555</v>
       </c>
       <c r="W92">
-        <v>0.2259389440254069</v>
+        <v>0.226047307277875</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.154887317792748</v>
+        <v>0.153185259355465</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2640570670925882</v>
+        <v>0.2659570670925882</v>
       </c>
       <c r="C93">
-        <v>-15.24737592412486</v>
+        <v>-15.55006918682517</v>
       </c>
       <c r="D93">
-        <v>5.885524075875141</v>
+        <v>5.834730813174836</v>
       </c>
       <c r="E93">
-        <v>20.0329</v>
+        <v>20.2848</v>
       </c>
       <c r="F93">
-        <v>22.9229</v>
+        <v>23.1748</v>
       </c>
       <c r="G93">
         <v>1.79</v>
@@ -8913,37 +8913,37 @@
         <v>0.828</v>
       </c>
       <c r="M93">
-        <v>5.405219820000001</v>
+        <v>5.464617840000001</v>
       </c>
       <c r="N93">
-        <v>-4.577219820000001</v>
+        <v>-4.63661784</v>
       </c>
       <c r="O93">
-        <v>-1.2358493514</v>
+        <v>-1.2518868168</v>
       </c>
       <c r="P93">
-        <v>-3.341370468600001</v>
+        <v>-3.384731023200001</v>
       </c>
       <c r="Q93">
-        <v>-3.2653704686</v>
+        <v>-3.3087310232</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.6483779718857996</v>
+        <v>0.7237002183715247</v>
       </c>
       <c r="T93">
-        <v>11.03642717173131</v>
+        <v>12.41598056819772</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.04136002002597555</v>
+        <v>0.0409104545909106</v>
       </c>
       <c r="W93">
-        <v>0.226047307277875</v>
+        <v>0.2261533148074633</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.153185259355465</v>
+        <v>0.1515202021885579</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2659570670925882</v>
+        <v>0.2678570670925882</v>
       </c>
       <c r="C94">
-        <v>-15.55006918682517</v>
+        <v>-15.85189323873751</v>
       </c>
       <c r="D94">
-        <v>5.834730813174836</v>
+        <v>5.784806761262495</v>
       </c>
       <c r="E94">
-        <v>20.2848</v>
+        <v>20.5367</v>
       </c>
       <c r="F94">
-        <v>23.1748</v>
+        <v>23.4267</v>
       </c>
       <c r="G94">
         <v>1.79</v>
@@ -8995,37 +8995,37 @@
         <v>0.828</v>
       </c>
       <c r="M94">
-        <v>5.464617840000001</v>
+        <v>5.524015860000001</v>
       </c>
       <c r="N94">
-        <v>-4.63661784</v>
+        <v>-4.696015860000001</v>
       </c>
       <c r="O94">
-        <v>-1.2518868168</v>
+        <v>-1.2679242822</v>
       </c>
       <c r="P94">
-        <v>-3.384731023200001</v>
+        <v>-3.428091577800001</v>
       </c>
       <c r="Q94">
-        <v>-3.3087310232</v>
+        <v>-3.352091577800001</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.7237002183715247</v>
+        <v>0.8205431067103139</v>
       </c>
       <c r="T94">
-        <v>12.41598056819772</v>
+        <v>14.18969207794025</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.0409104545909106</v>
+        <v>0.04047055722971801</v>
       </c>
       <c r="W94">
-        <v>0.2261533148074633</v>
+        <v>0.2262570426052325</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.1515202021885579</v>
+        <v>0.1498909527026594</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2678570670925882</v>
+        <v>0.2697570670925882</v>
       </c>
       <c r="C95">
-        <v>-15.85189323873751</v>
+        <v>-16.15287020241222</v>
       </c>
       <c r="D95">
-        <v>5.784806761262495</v>
+        <v>5.73572979758778</v>
       </c>
       <c r="E95">
-        <v>20.5367</v>
+        <v>20.7886</v>
       </c>
       <c r="F95">
-        <v>23.4267</v>
+        <v>23.6786</v>
       </c>
       <c r="G95">
         <v>1.79</v>
@@ -9077,37 +9077,37 @@
         <v>0.828</v>
       </c>
       <c r="M95">
-        <v>5.524015860000001</v>
+        <v>5.583413880000001</v>
       </c>
       <c r="N95">
-        <v>-4.696015860000001</v>
+        <v>-4.755413880000001</v>
       </c>
       <c r="O95">
-        <v>-1.2679242822</v>
+        <v>-1.2839617476</v>
       </c>
       <c r="P95">
-        <v>-3.428091577800001</v>
+        <v>-3.471452132400001</v>
       </c>
       <c r="Q95">
-        <v>-3.352091577800001</v>
+        <v>-3.3954521324</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.8205431067103139</v>
+        <v>0.9496669578287</v>
       </c>
       <c r="T95">
-        <v>14.18969207794025</v>
+        <v>16.55464075759697</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.04047055722971801</v>
+        <v>0.04004001938684867</v>
       </c>
       <c r="W95">
-        <v>0.2262570426052325</v>
+        <v>0.2263585634285811</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.1498909527026594</v>
+        <v>0.1482963680994396</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2697570670925882</v>
+        <v>0.2716570670925882</v>
       </c>
       <c r="C96">
-        <v>-16.15287020241222</v>
+        <v>-16.45302145598468</v>
       </c>
       <c r="D96">
-        <v>5.73572979758778</v>
+        <v>5.687478544015319</v>
       </c>
       <c r="E96">
-        <v>20.7886</v>
+        <v>21.0405</v>
       </c>
       <c r="F96">
-        <v>23.6786</v>
+        <v>23.9305</v>
       </c>
       <c r="G96">
         <v>1.79</v>
@@ -9159,37 +9159,37 @@
         <v>0.828</v>
       </c>
       <c r="M96">
-        <v>5.583413880000001</v>
+        <v>5.642811900000001</v>
       </c>
       <c r="N96">
-        <v>-4.755413880000001</v>
+        <v>-4.8148119</v>
       </c>
       <c r="O96">
-        <v>-1.2839617476</v>
+        <v>-1.299999213</v>
       </c>
       <c r="P96">
-        <v>-3.471452132400001</v>
+        <v>-3.514812687</v>
       </c>
       <c r="Q96">
-        <v>-3.3954521324</v>
+        <v>-3.438812687</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.9496669578287</v>
+        <v>1.130440349394441</v>
       </c>
       <c r="T96">
-        <v>16.55464075759697</v>
+        <v>19.86556890911637</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.04004001938684867</v>
+        <v>0.03961854549856606</v>
       </c>
       <c r="W96">
-        <v>0.2263585634285811</v>
+        <v>0.2264579469714381</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.1482963680994396</v>
+        <v>0.1467353536983929</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2716570670925882</v>
+        <v>0.2735570670925882</v>
       </c>
       <c r="C97">
-        <v>-16.45302145598468</v>
+        <v>-16.75236766422566</v>
       </c>
       <c r="D97">
-        <v>5.687478544015319</v>
+        <v>5.640032335774341</v>
       </c>
       <c r="E97">
-        <v>21.0405</v>
+        <v>21.2924</v>
       </c>
       <c r="F97">
-        <v>23.9305</v>
+        <v>24.1824</v>
       </c>
       <c r="G97">
         <v>1.79</v>
@@ -9241,37 +9241,37 @@
         <v>0.828</v>
       </c>
       <c r="M97">
-        <v>5.642811900000001</v>
+        <v>5.702209920000001</v>
       </c>
       <c r="N97">
-        <v>-4.8148119</v>
+        <v>-4.874209920000001</v>
       </c>
       <c r="O97">
-        <v>-1.299999213</v>
+        <v>-1.3160366784</v>
       </c>
       <c r="P97">
-        <v>-3.514812687</v>
+        <v>-3.5581732416</v>
       </c>
       <c r="Q97">
-        <v>-3.438812687</v>
+        <v>-3.4821732416</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.130440349394441</v>
+        <v>1.401600436743051</v>
       </c>
       <c r="T97">
-        <v>19.86556890911637</v>
+        <v>24.83196113639547</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.03961854549856606</v>
+        <v>0.03920585231628932</v>
       </c>
       <c r="W97">
-        <v>0.2264579469714381</v>
+        <v>0.226555260023819</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.1467353536983929</v>
+        <v>0.1452068604307012</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2735570670925882</v>
+        <v>0.2754570670925882</v>
       </c>
       <c r="C98">
-        <v>-16.75236766422566</v>
+        <v>-17.05092880805038</v>
       </c>
       <c r="D98">
-        <v>5.640032335774341</v>
+        <v>5.593371191949621</v>
       </c>
       <c r="E98">
-        <v>21.2924</v>
+        <v>21.5443</v>
       </c>
       <c r="F98">
-        <v>24.1824</v>
+        <v>24.4343</v>
       </c>
       <c r="G98">
         <v>1.79</v>
@@ -9323,37 +9323,37 @@
         <v>0.828</v>
       </c>
       <c r="M98">
-        <v>5.70220992</v>
+        <v>5.76160794</v>
       </c>
       <c r="N98">
-        <v>-4.87420992</v>
+        <v>-4.93360794</v>
       </c>
       <c r="O98">
-        <v>-1.3160366784</v>
+        <v>-1.3320741438</v>
       </c>
       <c r="P98">
-        <v>-3.5581732416</v>
+        <v>-3.6015337962</v>
       </c>
       <c r="Q98">
-        <v>-3.4821732416</v>
+        <v>-3.5255337962</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.401600436743047</v>
+        <v>1.853533915657397</v>
       </c>
       <c r="T98">
-        <v>24.83196113639541</v>
+        <v>33.10928151519388</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.03920585231628933</v>
+        <v>0.0388016682717915</v>
       </c>
       <c r="W98">
-        <v>0.226555260023819</v>
+        <v>0.2266505666215116</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.1452068604307013</v>
+        <v>0.1437098824881167</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2754570670925882</v>
+        <v>0.2773570670925882</v>
       </c>
       <c r="C99">
-        <v>-17.05092880805038</v>
+        <v>-17.3487242125748</v>
       </c>
       <c r="D99">
-        <v>5.593371191949621</v>
+        <v>5.547475787425194</v>
       </c>
       <c r="E99">
-        <v>21.5443</v>
+        <v>21.7962</v>
       </c>
       <c r="F99">
-        <v>24.4343</v>
+        <v>24.6862</v>
       </c>
       <c r="G99">
         <v>1.79</v>
@@ -9405,37 +9405,37 @@
         <v>0.828</v>
       </c>
       <c r="M99">
-        <v>5.76160794</v>
+        <v>5.82100596</v>
       </c>
       <c r="N99">
-        <v>-4.93360794</v>
+        <v>-4.99300596</v>
       </c>
       <c r="O99">
-        <v>-1.3320741438</v>
+        <v>-1.3481116092</v>
       </c>
       <c r="P99">
-        <v>-3.6015337962</v>
+        <v>-3.6448943508</v>
       </c>
       <c r="Q99">
-        <v>-3.5255337962</v>
+        <v>-3.5688943508</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.853533915657397</v>
+        <v>2.757400873486095</v>
       </c>
       <c r="T99">
-        <v>33.10928151519388</v>
+        <v>49.66392227279081</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.0388016682717915</v>
+        <v>0.03840573288126302</v>
       </c>
       <c r="W99">
-        <v>0.2266505666215116</v>
+        <v>0.2267439281865982</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.1437098824881167</v>
+        <v>0.142243455115789</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2773570670925882</v>
+        <v>0.2792570670925882</v>
       </c>
       <c r="C100">
-        <v>-17.3487242125748</v>
+        <v>-17.64577257380188</v>
       </c>
       <c r="D100">
-        <v>5.547475787425194</v>
+        <v>5.502327426198126</v>
       </c>
       <c r="E100">
-        <v>21.7962</v>
+        <v>22.0481</v>
       </c>
       <c r="F100">
-        <v>24.6862</v>
+        <v>24.9381</v>
       </c>
       <c r="G100">
         <v>1.79</v>
@@ -9487,37 +9487,37 @@
         <v>0.828</v>
       </c>
       <c r="M100">
-        <v>5.82100596</v>
+        <v>5.880403980000001</v>
       </c>
       <c r="N100">
-        <v>-4.99300596</v>
+        <v>-5.05240398</v>
       </c>
       <c r="O100">
-        <v>-1.3481116092</v>
+        <v>-1.3641490746</v>
       </c>
       <c r="P100">
-        <v>-3.6448943508</v>
+        <v>-3.6882549054</v>
       </c>
       <c r="Q100">
-        <v>-3.5688943508</v>
+        <v>-3.6122549054</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.757400873486095</v>
+        <v>5.469001746972189</v>
       </c>
       <c r="T100">
-        <v>49.66392227279081</v>
+        <v>99.32784454558163</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.03840573288126302</v>
+        <v>0.03801779618549268</v>
       </c>
       <c r="W100">
-        <v>0.2267439281865982</v>
+        <v>0.2268354036594608</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.142243455115789</v>
+        <v>0.1408066525388618</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2792570670925882</v>
-      </c>
-      <c r="C101">
-        <v>-17.64577257380188</v>
-      </c>
-      <c r="D101">
-        <v>5.502327426198126</v>
-      </c>
-      <c r="E101">
-        <v>22.0481</v>
-      </c>
-      <c r="F101">
-        <v>24.9381</v>
-      </c>
-      <c r="G101">
-        <v>1.79</v>
-      </c>
-      <c r="H101">
-        <v>22.3</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>0.904</v>
-      </c>
-      <c r="K101">
-        <v>0.07600000000000007</v>
-      </c>
-      <c r="L101">
-        <v>0.828</v>
-      </c>
-      <c r="M101">
-        <v>5.880403980000001</v>
-      </c>
-      <c r="N101">
-        <v>-5.05240398</v>
-      </c>
-      <c r="O101">
-        <v>-1.3641490746</v>
-      </c>
-      <c r="P101">
-        <v>-3.6882549054</v>
-      </c>
-      <c r="Q101">
-        <v>-3.6122549054</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>5.469001746972189</v>
-      </c>
-      <c r="T101">
-        <v>99.32784454558163</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.03801779618549268</v>
-      </c>
-      <c r="W101">
-        <v>0.2268354036594608</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.1408066525388618</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
